--- a/data/climate_data/indicateurs_journaliers_par_essais/1.1.4.2.6_R2016/191025_INRA16_IPC_Calcul_ok.xlsx
+++ b/data/climate_data/indicateurs_journaliers_par_essais/1.1.4.2.6_R2016/191025_INRA16_IPC_Calcul_ok.xlsx
@@ -1293,9 +1293,9 @@
         <f aca="false">J6-R6</f>
         <v>-1.33</v>
       </c>
-      <c r="T6" s="13" t="e">
-        <f aca="false">#REF!+S6</f>
-        <v>#REF!</v>
+      <c r="T6" s="13" t="n">
+        <f aca="false">29.3+S6</f>
+        <v>27.97</v>
       </c>
       <c r="U6" s="12" t="s">
         <v>29</v>
@@ -1372,9 +1372,9 @@
         <f aca="false">J7-R7</f>
         <v>-1.295</v>
       </c>
-      <c r="T7" s="13" t="e">
+      <c r="T7" s="13" t="n">
         <f aca="false">MIN(197.4,(T6+S7))</f>
-        <v>#REF!</v>
+        <v>26.675</v>
       </c>
       <c r="U7" s="8" t="n">
         <v>68</v>
@@ -1450,9 +1450,9 @@
         <f aca="false">J8-R8</f>
         <v>2.735</v>
       </c>
-      <c r="T8" s="13" t="e">
+      <c r="T8" s="13" t="n">
         <f aca="false">MIN(197.4,(T7+S8))</f>
-        <v>#REF!</v>
+        <v>29.41</v>
       </c>
       <c r="U8" s="12" t="s">
         <v>32</v>
@@ -1529,9 +1529,9 @@
         <f aca="false">J9-R9</f>
         <v>0.725</v>
       </c>
-      <c r="T9" s="13" t="e">
+      <c r="T9" s="13" t="n">
         <f aca="false">MIN(197.4,(T8+S9))</f>
-        <v>#REF!</v>
+        <v>30.135</v>
       </c>
       <c r="U9" s="8" t="n">
         <v>0</v>
@@ -1608,9 +1608,9 @@
         <f aca="false">J10-R10</f>
         <v>4.95</v>
       </c>
-      <c r="T10" s="13" t="e">
+      <c r="T10" s="13" t="n">
         <f aca="false">MIN(197.4,(T9+S10))</f>
-        <v>#REF!</v>
+        <v>35.085</v>
       </c>
       <c r="U10" s="12" t="s">
         <v>35</v>
@@ -1687,9 +1687,9 @@
         <f aca="false">J11-R11</f>
         <v>2.46</v>
       </c>
-      <c r="T11" s="13" t="e">
+      <c r="T11" s="13" t="n">
         <f aca="false">MIN(197.4,(T10+S11))</f>
-        <v>#REF!</v>
+        <v>37.545</v>
       </c>
       <c r="U11" s="8" t="n">
         <v>50</v>
@@ -1765,9 +1765,9 @@
         <f aca="false">J12-R12</f>
         <v>14.995</v>
       </c>
-      <c r="T12" s="13" t="e">
+      <c r="T12" s="13" t="n">
         <f aca="false">MIN(197.4,(T11+S12))</f>
-        <v>#REF!</v>
+        <v>52.54</v>
       </c>
       <c r="U12" s="12" t="s">
         <v>38</v>
@@ -1840,13 +1840,13 @@
         <f aca="false">J13-R13</f>
         <v>9.735</v>
       </c>
-      <c r="T13" s="13" t="e">
+      <c r="T13" s="13" t="n">
         <f aca="false">MIN(197.4,(T12+S13))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U13" s="13" t="e">
+        <v>62.275</v>
+      </c>
+      <c r="U13" s="13" t="n">
         <f aca="false">MIN(T6:T131)</f>
-        <v>#REF!</v>
+        <v>26.675</v>
       </c>
       <c r="V13" s="8" t="n">
         <v>540.8</v>
@@ -1916,9 +1916,9 @@
         <f aca="false">J14-R14</f>
         <v>0.53</v>
       </c>
-      <c r="T14" s="13" t="e">
+      <c r="T14" s="13" t="n">
         <f aca="false">MIN(197.4,(T13+S14))</f>
-        <v>#REF!</v>
+        <v>62.805</v>
       </c>
       <c r="U14" s="12" t="s">
         <v>40</v>
@@ -1992,13 +1992,13 @@
         <f aca="false">J15-R15</f>
         <v>1.38888888888889</v>
       </c>
-      <c r="T15" s="13" t="e">
+      <c r="T15" s="13" t="n">
         <f aca="false">MIN(197.4,(T14+S15))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U15" s="13" t="e">
+        <v>64.1938888888889</v>
+      </c>
+      <c r="U15" s="13" t="n">
         <f aca="false">MAX(T6:T131)</f>
-        <v>#REF!</v>
+        <v>170.28</v>
       </c>
       <c r="V15" s="8" t="n">
         <v>940</v>
@@ -2069,9 +2069,9 @@
         <f aca="false">J16-R16</f>
         <v>-0.477777777777778</v>
       </c>
-      <c r="T16" s="13" t="e">
+      <c r="T16" s="13" t="n">
         <f aca="false">MIN(197.4,(T15+S16))</f>
-        <v>#REF!</v>
+        <v>63.7161111111111</v>
       </c>
       <c r="U16" s="12" t="s">
         <v>42</v>
@@ -2145,13 +2145,13 @@
         <f aca="false">J17-R17</f>
         <v>-0.623333333333333</v>
       </c>
-      <c r="T17" s="13" t="e">
+      <c r="T17" s="13" t="n">
         <f aca="false">MIN(197.4,(T16+S17))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U17" s="14" t="e">
+        <v>63.0927777777778</v>
+      </c>
+      <c r="U17" s="14" t="n">
         <f aca="false">AVERAGE(T6:T131)</f>
-        <v>#REF!</v>
+        <v>87.6637257495591</v>
       </c>
       <c r="V17" s="8" t="n">
         <v>1099.9</v>
@@ -2222,9 +2222,9 @@
         <f aca="false">J18-R18</f>
         <v>2.89055555555556</v>
       </c>
-      <c r="T18" s="13" t="e">
+      <c r="T18" s="13" t="n">
         <f aca="false">MIN(197.4,(T17+S18))</f>
-        <v>#REF!</v>
+        <v>65.9833333333333</v>
       </c>
       <c r="V18" s="8" t="n">
         <v>401.6</v>
@@ -2295,13 +2295,13 @@
         <f aca="false">J19-R19</f>
         <v>0.244444444444444</v>
       </c>
-      <c r="T19" s="13" t="e">
+      <c r="T19" s="13" t="n">
         <f aca="false">MIN(197.4,(T18+S19))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U19" s="13" t="e">
+        <v>66.2277777777778</v>
+      </c>
+      <c r="U19" s="13" t="n">
         <f aca="false">(U17*100)/197.4</f>
-        <v>#REF!</v>
+        <v>44.4091822439509</v>
       </c>
       <c r="V19" s="8" t="n">
         <v>891.3</v>
@@ -2369,9 +2369,9 @@
         <f aca="false">J20-R20</f>
         <v>-0.481666666666666</v>
       </c>
-      <c r="T20" s="13" t="e">
+      <c r="T20" s="13" t="n">
         <f aca="false">MIN(197.4,(T19+S20))</f>
-        <v>#REF!</v>
+        <v>65.7461111111111</v>
       </c>
       <c r="V20" s="8" t="n">
         <v>1462.5</v>
@@ -2439,9 +2439,9 @@
         <f aca="false">J21-R21</f>
         <v>-0.427777777777778</v>
       </c>
-      <c r="T21" s="13" t="e">
+      <c r="T21" s="13" t="n">
         <f aca="false">MIN(197.4,(T20+S21))</f>
-        <v>#REF!</v>
+        <v>65.3183333333333</v>
       </c>
       <c r="V21" s="8" t="n">
         <v>410</v>
@@ -2509,9 +2509,9 @@
         <f aca="false">J22-R22</f>
         <v>-0.688888888888889</v>
       </c>
-      <c r="T22" s="13" t="e">
+      <c r="T22" s="13" t="n">
         <f aca="false">MIN(197.4,(T21+S22))</f>
-        <v>#REF!</v>
+        <v>64.6294444444445</v>
       </c>
       <c r="V22" s="8" t="n">
         <v>1137.9</v>
@@ -2579,9 +2579,9 @@
         <f aca="false">J23-R23</f>
         <v>-0.72</v>
       </c>
-      <c r="T23" s="13" t="e">
+      <c r="T23" s="13" t="n">
         <f aca="false">MIN(197.4,(T22+S23))</f>
-        <v>#REF!</v>
+        <v>63.9094444444444</v>
       </c>
       <c r="V23" s="8" t="n">
         <v>1070.7</v>
@@ -2649,9 +2649,9 @@
         <f aca="false">J24-R24</f>
         <v>-1.25722222222222</v>
       </c>
-      <c r="T24" s="13" t="e">
+      <c r="T24" s="13" t="n">
         <f aca="false">MIN(197.4,(T23+S24))</f>
-        <v>#REF!</v>
+        <v>62.6522222222222</v>
       </c>
       <c r="V24" s="8" t="n">
         <v>1573.4</v>
@@ -2719,9 +2719,9 @@
         <f aca="false">J25-R25</f>
         <v>-1.60333333333333</v>
       </c>
-      <c r="T25" s="13" t="e">
+      <c r="T25" s="13" t="n">
         <f aca="false">MIN(197.4,(T24+S25))</f>
-        <v>#REF!</v>
+        <v>61.0488888888889</v>
       </c>
       <c r="V25" s="8" t="n">
         <v>1799</v>
@@ -2789,9 +2789,9 @@
         <f aca="false">J26-R26</f>
         <v>-1.625</v>
       </c>
-      <c r="T26" s="13" t="e">
+      <c r="T26" s="13" t="n">
         <f aca="false">MIN(197.4,(T25+S26))</f>
-        <v>#REF!</v>
+        <v>59.4238888888889</v>
       </c>
       <c r="V26" s="8" t="n">
         <v>1804.5</v>
@@ -2859,9 +2859,9 @@
         <f aca="false">J27-R27</f>
         <v>-1.35111111111111</v>
       </c>
-      <c r="T27" s="13" t="e">
+      <c r="T27" s="13" t="n">
         <f aca="false">MIN(197.4,(T26+S27))</f>
-        <v>#REF!</v>
+        <v>58.0727777777778</v>
       </c>
       <c r="V27" s="8" t="n">
         <v>1792.8</v>
@@ -2929,9 +2929,9 @@
         <f aca="false">J28-R28</f>
         <v>-1.45444444444444</v>
       </c>
-      <c r="T28" s="13" t="e">
+      <c r="T28" s="13" t="n">
         <f aca="false">MIN(197.4,(T27+S28))</f>
-        <v>#REF!</v>
+        <v>56.6183333333334</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>1741.6</v>
@@ -2999,9 +2999,9 @@
         <f aca="false">J29-R29</f>
         <v>-1.08333333333333</v>
       </c>
-      <c r="T29" s="13" t="e">
+      <c r="T29" s="13" t="n">
         <f aca="false">MIN(197.4,(T28+S29))</f>
-        <v>#REF!</v>
+        <v>55.535</v>
       </c>
       <c r="V29" s="8" t="n">
         <v>1537.5</v>
@@ -3069,9 +3069,9 @@
         <f aca="false">J30-R30</f>
         <v>-0.307222222222222</v>
       </c>
-      <c r="T30" s="13" t="e">
+      <c r="T30" s="13" t="n">
         <f aca="false">MIN(197.4,(T29+S30))</f>
-        <v>#REF!</v>
+        <v>55.2277777777778</v>
       </c>
       <c r="V30" s="8" t="n">
         <v>326.6</v>
@@ -3139,9 +3139,9 @@
         <f aca="false">J31-R31</f>
         <v>6.13333333333333</v>
       </c>
-      <c r="T31" s="13" t="e">
+      <c r="T31" s="13" t="n">
         <f aca="false">MIN(197.4,(T30+S31))</f>
-        <v>#REF!</v>
+        <v>61.3611111111111</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>728.7</v>
@@ -3209,9 +3209,9 @@
         <f aca="false">J32-R32</f>
         <v>7.31</v>
       </c>
-      <c r="T32" s="13" t="e">
+      <c r="T32" s="13" t="n">
         <f aca="false">MIN(197.4,(T31+S32))</f>
-        <v>#REF!</v>
+        <v>68.6711111111111</v>
       </c>
       <c r="V32" s="8" t="n">
         <v>277.2</v>
@@ -3279,9 +3279,9 @@
         <f aca="false">J33-R33</f>
         <v>0.0800000000000001</v>
       </c>
-      <c r="T33" s="13" t="e">
+      <c r="T33" s="13" t="n">
         <f aca="false">MIN(197.4,(T32+S33))</f>
-        <v>#REF!</v>
+        <v>68.7511111111111</v>
       </c>
       <c r="V33" s="8" t="n">
         <v>355.9</v>
@@ -3349,9 +3349,9 @@
         <f aca="false">J34-R34</f>
         <v>-0.876111111111111</v>
       </c>
-      <c r="T34" s="13" t="e">
+      <c r="T34" s="13" t="n">
         <f aca="false">MIN(197.4,(T33+S34))</f>
-        <v>#REF!</v>
+        <v>67.875</v>
       </c>
       <c r="V34" s="8" t="n">
         <v>1086.8</v>
@@ -3419,9 +3419,9 @@
         <f aca="false">J35-R35</f>
         <v>-0.466666666666667</v>
       </c>
-      <c r="T35" s="13" t="e">
+      <c r="T35" s="13" t="n">
         <f aca="false">MIN(197.4,(T34+S35))</f>
-        <v>#REF!</v>
+        <v>67.4083333333334</v>
       </c>
       <c r="V35" s="8" t="n">
         <v>868.4</v>
@@ -3489,9 +3489,9 @@
         <f aca="false">J36-R36</f>
         <v>-0.802777777777778</v>
       </c>
-      <c r="T36" s="13" t="e">
+      <c r="T36" s="13" t="n">
         <f aca="false">MIN(197.4,(T35+S36))</f>
-        <v>#REF!</v>
+        <v>66.6055555555556</v>
       </c>
       <c r="V36" s="8" t="n">
         <v>1119.6</v>
@@ -3559,9 +3559,9 @@
         <f aca="false">J37-R37</f>
         <v>-0.668888888888889</v>
       </c>
-      <c r="T37" s="13" t="e">
+      <c r="T37" s="13" t="n">
         <f aca="false">MIN(197.4,(T36+S37))</f>
-        <v>#REF!</v>
+        <v>65.9366666666667</v>
       </c>
       <c r="V37" s="8" t="n">
         <v>828.2</v>
@@ -3629,9 +3629,9 @@
         <f aca="false">J38-R38</f>
         <v>-1.06333333333333</v>
       </c>
-      <c r="T38" s="13" t="e">
+      <c r="T38" s="13" t="n">
         <f aca="false">MIN(197.4,(T37+S38))</f>
-        <v>#REF!</v>
+        <v>64.8733333333334</v>
       </c>
       <c r="V38" s="8" t="n">
         <v>1103.7</v>
@@ -3699,9 +3699,9 @@
         <f aca="false">J39-R39</f>
         <v>-0.782222222222222</v>
       </c>
-      <c r="T39" s="13" t="e">
+      <c r="T39" s="13" t="n">
         <f aca="false">MIN(197.4,(T38+S39))</f>
-        <v>#REF!</v>
+        <v>64.0911111111111</v>
       </c>
       <c r="V39" s="8" t="n">
         <v>676.5</v>
@@ -3769,9 +3769,9 @@
         <f aca="false">J40-R40</f>
         <v>-0.791111111111111</v>
       </c>
-      <c r="T40" s="13" t="e">
+      <c r="T40" s="13" t="n">
         <f aca="false">MIN(197.4,(T39+S40))</f>
-        <v>#REF!</v>
+        <v>63.3</v>
       </c>
       <c r="V40" s="8" t="n">
         <v>948.4</v>
@@ -3839,9 +3839,9 @@
         <f aca="false">J41-R41</f>
         <v>-0.65</v>
       </c>
-      <c r="T41" s="13" t="e">
+      <c r="T41" s="13" t="n">
         <f aca="false">MIN(197.4,(T40+S41))</f>
-        <v>#REF!</v>
+        <v>62.65</v>
       </c>
       <c r="V41" s="8" t="n">
         <v>627</v>
@@ -3909,9 +3909,9 @@
         <f aca="false">J42-R42</f>
         <v>-0.758333333333333</v>
       </c>
-      <c r="T42" s="13" t="e">
+      <c r="T42" s="13" t="n">
         <f aca="false">MIN(197.4,(T41+S42))</f>
-        <v>#REF!</v>
+        <v>61.8916666666667</v>
       </c>
       <c r="V42" s="8" t="n">
         <v>970.6</v>
@@ -3979,9 +3979,9 @@
         <f aca="false">J43-R43</f>
         <v>-0.255555555555556</v>
       </c>
-      <c r="T43" s="13" t="e">
+      <c r="T43" s="13" t="n">
         <f aca="false">MIN(197.4,(T42+S43))</f>
-        <v>#REF!</v>
+        <v>61.6361111111111</v>
       </c>
       <c r="V43" s="8" t="n">
         <v>335</v>
@@ -4049,9 +4049,9 @@
         <f aca="false">J44-R44</f>
         <v>-0.62</v>
       </c>
-      <c r="T44" s="13" t="e">
+      <c r="T44" s="13" t="n">
         <f aca="false">MIN(197.4,(T43+S44))</f>
-        <v>#REF!</v>
+        <v>61.0161111111111</v>
       </c>
       <c r="V44" s="8" t="n">
         <v>583.4</v>
@@ -4119,9 +4119,9 @@
         <f aca="false">J45-R45</f>
         <v>-0.365555555555555</v>
       </c>
-      <c r="T45" s="13" t="e">
+      <c r="T45" s="13" t="n">
         <f aca="false">MIN(197.4,(T44+S45))</f>
-        <v>#REF!</v>
+        <v>60.6505555555556</v>
       </c>
       <c r="V45" s="8" t="n">
         <v>522</v>
@@ -4189,9 +4189,9 @@
         <f aca="false">J46-R46</f>
         <v>-0.95</v>
       </c>
-      <c r="T46" s="13" t="e">
+      <c r="T46" s="13" t="n">
         <f aca="false">MIN(197.4,(T45+S46))</f>
-        <v>#REF!</v>
+        <v>59.7005555555556</v>
       </c>
       <c r="V46" s="8" t="n">
         <v>1146.4</v>
@@ -4259,9 +4259,9 @@
         <f aca="false">J47-R47</f>
         <v>-0.48</v>
       </c>
-      <c r="T47" s="13" t="e">
+      <c r="T47" s="13" t="n">
         <f aca="false">MIN(197.4,(T46+S47))</f>
-        <v>#REF!</v>
+        <v>59.2205555555556</v>
       </c>
       <c r="V47" s="8" t="n">
         <v>366.6</v>
@@ -4329,9 +4329,9 @@
         <f aca="false">J48-R48</f>
         <v>1.48444444444444</v>
       </c>
-      <c r="T48" s="13" t="e">
+      <c r="T48" s="13" t="n">
         <f aca="false">MIN(197.4,(T47+S48))</f>
-        <v>#REF!</v>
+        <v>60.705</v>
       </c>
       <c r="V48" s="8" t="n">
         <v>187</v>
@@ -4399,9 +4399,9 @@
         <f aca="false">J49-R49</f>
         <v>-0.281111111111111</v>
       </c>
-      <c r="T49" s="13" t="e">
+      <c r="T49" s="13" t="n">
         <f aca="false">MIN(197.4,(T48+S49))</f>
-        <v>#REF!</v>
+        <v>60.4238888888889</v>
       </c>
       <c r="V49" s="8" t="n">
         <v>185.7</v>
@@ -4469,9 +4469,9 @@
         <f aca="false">J50-R50</f>
         <v>-0.495</v>
       </c>
-      <c r="T50" s="13" t="e">
+      <c r="T50" s="13" t="n">
         <f aca="false">MIN(197.4,(T49+S50))</f>
-        <v>#REF!</v>
+        <v>59.9288888888889</v>
       </c>
       <c r="V50" s="8" t="n">
         <v>184.6</v>
@@ -4539,9 +4539,9 @@
         <f aca="false">J51-R51</f>
         <v>0.566666666666667</v>
       </c>
-      <c r="T51" s="13" t="e">
+      <c r="T51" s="13" t="n">
         <f aca="false">MIN(197.4,(T50+S51))</f>
-        <v>#REF!</v>
+        <v>60.4955555555556</v>
       </c>
       <c r="V51" s="8" t="n">
         <v>271.7</v>
@@ -4609,9 +4609,9 @@
         <f aca="false">J52-R52</f>
         <v>-0.841666666666667</v>
       </c>
-      <c r="T52" s="13" t="e">
+      <c r="T52" s="13" t="n">
         <f aca="false">MIN(197.4,(T51+S52))</f>
-        <v>#REF!</v>
+        <v>59.6538888888889</v>
       </c>
       <c r="V52" s="8" t="n">
         <v>884.8</v>
@@ -4679,9 +4679,9 @@
         <f aca="false">J53-R53</f>
         <v>1.33333333333333</v>
       </c>
-      <c r="T53" s="13" t="e">
+      <c r="T53" s="13" t="n">
         <f aca="false">MIN(197.4,(T52+S53))</f>
-        <v>#REF!</v>
+        <v>60.9872222222223</v>
       </c>
       <c r="V53" s="8" t="n">
         <v>704.4</v>
@@ -4749,9 +4749,9 @@
         <f aca="false">J54-R54</f>
         <v>4.61388888888889</v>
       </c>
-      <c r="T54" s="13" t="e">
+      <c r="T54" s="13" t="n">
         <f aca="false">MIN(197.4,(T53+S54))</f>
-        <v>#REF!</v>
+        <v>65.6011111111111</v>
       </c>
       <c r="V54" s="8" t="n">
         <v>139.8</v>
@@ -4819,9 +4819,9 @@
         <f aca="false">J55-R55</f>
         <v>-0.0888888888888889</v>
       </c>
-      <c r="T55" s="13" t="e">
+      <c r="T55" s="13" t="n">
         <f aca="false">MIN(197.4,(T54+S55))</f>
-        <v>#REF!</v>
+        <v>65.5122222222223</v>
       </c>
       <c r="V55" s="8" t="n">
         <v>298</v>
@@ -4889,9 +4889,9 @@
         <f aca="false">J56-R56</f>
         <v>0.208333333333333</v>
       </c>
-      <c r="T56" s="13" t="e">
+      <c r="T56" s="13" t="n">
         <f aca="false">MIN(197.4,(T55+S56))</f>
-        <v>#REF!</v>
+        <v>65.7205555555556</v>
       </c>
       <c r="V56" s="8" t="n">
         <v>177.4</v>
@@ -4959,9 +4959,9 @@
         <f aca="false">J57-R57</f>
         <v>-0.824444444444444</v>
       </c>
-      <c r="T57" s="13" t="e">
+      <c r="T57" s="13" t="n">
         <f aca="false">MIN(197.4,(T56+S57))</f>
-        <v>#REF!</v>
+        <v>64.8961111111111</v>
       </c>
       <c r="V57" s="8" t="n">
         <v>267.5</v>
@@ -5029,9 +5029,9 @@
         <f aca="false">J58-R58</f>
         <v>-1.30777777777778</v>
       </c>
-      <c r="T58" s="13" t="e">
+      <c r="T58" s="13" t="n">
         <f aca="false">MIN(197.4,(T57+S58))</f>
-        <v>#REF!</v>
+        <v>63.5883333333334</v>
       </c>
       <c r="V58" s="8" t="n">
         <v>1058.3</v>
@@ -5099,9 +5099,9 @@
         <f aca="false">J59-R59</f>
         <v>-1.16</v>
       </c>
-      <c r="T59" s="13" t="e">
+      <c r="T59" s="13" t="n">
         <f aca="false">MIN(197.4,(T58+S59))</f>
-        <v>#REF!</v>
+        <v>62.4283333333334</v>
       </c>
       <c r="V59" s="8" t="n">
         <v>1041.5</v>
@@ -5169,9 +5169,9 @@
         <f aca="false">J60-R60</f>
         <v>-0.771666666666667</v>
       </c>
-      <c r="T60" s="13" t="e">
+      <c r="T60" s="13" t="n">
         <f aca="false">MIN(197.4,(T59+S60))</f>
-        <v>#REF!</v>
+        <v>61.6566666666667</v>
       </c>
       <c r="V60" s="8" t="n">
         <v>1016.1</v>
@@ -5239,9 +5239,9 @@
         <f aca="false">J61-R61</f>
         <v>0.566666666666667</v>
       </c>
-      <c r="T61" s="13" t="e">
+      <c r="T61" s="13" t="n">
         <f aca="false">MIN(197.4,(T60+S61))</f>
-        <v>#REF!</v>
+        <v>62.2233333333334</v>
       </c>
       <c r="V61" s="8" t="n">
         <v>312.4</v>
@@ -5309,9 +5309,9 @@
         <f aca="false">J62-R62</f>
         <v>0.0449999999999999</v>
       </c>
-      <c r="T62" s="13" t="e">
+      <c r="T62" s="13" t="n">
         <f aca="false">MIN(197.4,(T61+S62))</f>
-        <v>#REF!</v>
+        <v>62.2683333333334</v>
       </c>
       <c r="V62" s="8" t="n">
         <v>564</v>
@@ -5379,9 +5379,9 @@
         <f aca="false">J63-R63</f>
         <v>2.95111111111111</v>
       </c>
-      <c r="T63" s="13" t="e">
+      <c r="T63" s="13" t="n">
         <f aca="false">MIN(197.4,(T62+S63))</f>
-        <v>#REF!</v>
+        <v>65.2194444444445</v>
       </c>
       <c r="V63" s="8" t="n">
         <v>159.6</v>
@@ -5449,9 +5449,9 @@
         <f aca="false">J64-R64</f>
         <v>8.98611111111111</v>
       </c>
-      <c r="T64" s="13" t="e">
+      <c r="T64" s="13" t="n">
         <f aca="false">MIN(197.4,(T63+S64))</f>
-        <v>#REF!</v>
+        <v>74.2055555555556</v>
       </c>
       <c r="V64" s="8" t="n">
         <v>98.3</v>
@@ -5519,9 +5519,9 @@
         <f aca="false">J65-R65</f>
         <v>-0.523333333333333</v>
       </c>
-      <c r="T65" s="13" t="e">
+      <c r="T65" s="13" t="n">
         <f aca="false">MIN(197.4,(T64+S65))</f>
-        <v>#REF!</v>
+        <v>73.6822222222223</v>
       </c>
       <c r="V65" s="8" t="n">
         <v>510.3</v>
@@ -5589,9 +5589,9 @@
         <f aca="false">J66-R66</f>
         <v>-0.447222222222222</v>
       </c>
-      <c r="T66" s="13" t="e">
+      <c r="T66" s="13" t="n">
         <f aca="false">MIN(197.4,(T65+S66))</f>
-        <v>#REF!</v>
+        <v>73.235</v>
       </c>
       <c r="V66" s="8" t="n">
         <v>148.5</v>
@@ -5659,9 +5659,9 @@
         <f aca="false">J67-R67</f>
         <v>-0.966666666666667</v>
       </c>
-      <c r="T67" s="13" t="e">
+      <c r="T67" s="13" t="n">
         <f aca="false">MIN(197.4,(T66+S67))</f>
-        <v>#REF!</v>
+        <v>72.2683333333334</v>
       </c>
       <c r="V67" s="8" t="n">
         <v>792.9</v>
@@ -5729,9 +5729,9 @@
         <f aca="false">J68-R68</f>
         <v>-0.42</v>
       </c>
-      <c r="T68" s="13" t="e">
+      <c r="T68" s="13" t="n">
         <f aca="false">MIN(197.4,(T67+S68))</f>
-        <v>#REF!</v>
+        <v>71.8483333333334</v>
       </c>
       <c r="V68" s="8" t="n">
         <v>273.1</v>
@@ -5799,9 +5799,9 @@
         <f aca="false">J69-R69</f>
         <v>0.537777777777778</v>
       </c>
-      <c r="T69" s="13" t="e">
+      <c r="T69" s="13" t="n">
         <f aca="false">MIN(197.4,(T68+S69))</f>
-        <v>#REF!</v>
+        <v>72.3861111111112</v>
       </c>
       <c r="V69" s="8" t="n">
         <v>164.9</v>
@@ -5869,9 +5869,9 @@
         <f aca="false">J70-R70</f>
         <v>0.235555555555556</v>
       </c>
-      <c r="T70" s="13" t="e">
+      <c r="T70" s="13" t="n">
         <f aca="false">MIN(197.4,(T69+S70))</f>
-        <v>#REF!</v>
+        <v>72.6216666666667</v>
       </c>
       <c r="V70" s="8" t="n">
         <v>302.5</v>
@@ -5939,9 +5939,9 @@
         <f aca="false">J71-R71</f>
         <v>-0.866666666666667</v>
       </c>
-      <c r="T71" s="13" t="e">
+      <c r="T71" s="13" t="n">
         <f aca="false">MIN(197.4,(T70+S71))</f>
-        <v>#REF!</v>
+        <v>71.755</v>
       </c>
       <c r="V71" s="8" t="n">
         <v>588.1</v>
@@ -6009,9 +6009,9 @@
         <f aca="false">J72-R72</f>
         <v>-0.537777777777778</v>
       </c>
-      <c r="T72" s="13" t="e">
+      <c r="T72" s="13" t="n">
         <f aca="false">MIN(197.4,(T71+S72))</f>
-        <v>#REF!</v>
+        <v>71.2172222222223</v>
       </c>
       <c r="V72" s="8" t="n">
         <v>401.8</v>
@@ -6079,9 +6079,9 @@
         <f aca="false">J73-R73</f>
         <v>-1.28777777777778</v>
       </c>
-      <c r="T73" s="13" t="e">
+      <c r="T73" s="13" t="n">
         <f aca="false">MIN(197.4,(T72+S73))</f>
-        <v>#REF!</v>
+        <v>69.9294444444445</v>
       </c>
       <c r="V73" s="8" t="n">
         <v>689.7</v>
@@ -6149,9 +6149,9 @@
         <f aca="false">J74-R74</f>
         <v>3.585</v>
       </c>
-      <c r="T74" s="13" t="e">
+      <c r="T74" s="13" t="n">
         <f aca="false">MIN(197.4,(T73+S74))</f>
-        <v>#REF!</v>
+        <v>73.5144444444445</v>
       </c>
       <c r="V74" s="8" t="n">
         <v>142</v>
@@ -6219,9 +6219,9 @@
         <f aca="false">J75-R75</f>
         <v>0.517777777777778</v>
       </c>
-      <c r="T75" s="13" t="e">
+      <c r="T75" s="13" t="n">
         <f aca="false">MIN(197.4,(T74+S75))</f>
-        <v>#REF!</v>
+        <v>74.0322222222223</v>
       </c>
       <c r="V75" s="8" t="n">
         <v>103.9</v>
@@ -6289,9 +6289,9 @@
         <f aca="false">J76-R76</f>
         <v>-0.625</v>
       </c>
-      <c r="T76" s="13" t="e">
+      <c r="T76" s="13" t="n">
         <f aca="false">MIN(197.4,(T75+S76))</f>
-        <v>#REF!</v>
+        <v>73.4072222222223</v>
       </c>
       <c r="V76" s="8" t="n">
         <v>179.5</v>
@@ -6359,9 +6359,9 @@
         <f aca="false">J77-R77</f>
         <v>10.11</v>
       </c>
-      <c r="T77" s="13" t="e">
+      <c r="T77" s="13" t="n">
         <f aca="false">MIN(197.4,(T76+S77))</f>
-        <v>#REF!</v>
+        <v>83.5172222222223</v>
       </c>
       <c r="V77" s="8" t="n">
         <v>121.3</v>
@@ -6429,9 +6429,9 @@
         <f aca="false">J78-R78</f>
         <v>14.1177777777778</v>
       </c>
-      <c r="T78" s="13" t="e">
+      <c r="T78" s="13" t="n">
         <f aca="false">MIN(197.4,(T77+S78))</f>
-        <v>#REF!</v>
+        <v>97.6350000000001</v>
       </c>
       <c r="V78" s="8" t="n">
         <v>129.3</v>
@@ -6499,9 +6499,9 @@
         <f aca="false">J79-R79</f>
         <v>4.10222222222222</v>
       </c>
-      <c r="T79" s="13" t="e">
+      <c r="T79" s="13" t="n">
         <f aca="false">MIN(197.4,(T78+S79))</f>
-        <v>#REF!</v>
+        <v>101.737222222222</v>
       </c>
       <c r="V79" s="8" t="n">
         <v>149.4</v>
@@ -6569,9 +6569,9 @@
         <f aca="false">J80-R80</f>
         <v>0.513333333333333</v>
       </c>
-      <c r="T80" s="13" t="e">
+      <c r="T80" s="13" t="n">
         <f aca="false">MIN(197.4,(T79+S80))</f>
-        <v>#REF!</v>
+        <v>102.250555555556</v>
       </c>
       <c r="V80" s="8" t="n">
         <v>596.4</v>
@@ -6639,9 +6639,9 @@
         <f aca="false">J81-R81</f>
         <v>0.822222222222222</v>
       </c>
-      <c r="T81" s="13" t="e">
+      <c r="T81" s="13" t="n">
         <f aca="false">MIN(197.4,(T80+S81))</f>
-        <v>#REF!</v>
+        <v>103.072777777778</v>
       </c>
       <c r="V81" s="8" t="n">
         <v>670.5</v>
@@ -6709,9 +6709,9 @@
         <f aca="false">J82-R82</f>
         <v>4.05444444444445</v>
       </c>
-      <c r="T82" s="13" t="e">
+      <c r="T82" s="13" t="n">
         <f aca="false">MIN(197.4,(T81+S82))</f>
-        <v>#REF!</v>
+        <v>107.127222222222</v>
       </c>
       <c r="V82" s="8" t="n">
         <v>97.1</v>
@@ -6779,9 +6779,9 @@
         <f aca="false">J83-R83</f>
         <v>2.83333333333333</v>
       </c>
-      <c r="T83" s="13" t="e">
+      <c r="T83" s="13" t="n">
         <f aca="false">MIN(197.4,(T82+S83))</f>
-        <v>#REF!</v>
+        <v>109.960555555556</v>
       </c>
       <c r="V83" s="8" t="n">
         <v>132.2</v>
@@ -6849,9 +6849,9 @@
         <f aca="false">J84-R84</f>
         <v>0.204444444444444</v>
       </c>
-      <c r="T84" s="13" t="e">
+      <c r="T84" s="13" t="n">
         <f aca="false">MIN(197.4,(T83+S84))</f>
-        <v>#REF!</v>
+        <v>110.165</v>
       </c>
       <c r="V84" s="8" t="n">
         <v>68.1</v>
@@ -6919,9 +6919,9 @@
         <f aca="false">J85-R85</f>
         <v>1.10222222222222</v>
       </c>
-      <c r="T85" s="13" t="e">
+      <c r="T85" s="13" t="n">
         <f aca="false">MIN(197.4,(T84+S85))</f>
-        <v>#REF!</v>
+        <v>111.267222222222</v>
       </c>
       <c r="V85" s="8" t="n">
         <v>140.5</v>
@@ -6989,9 +6989,9 @@
         <f aca="false">J86-R86</f>
         <v>-0.675</v>
       </c>
-      <c r="T86" s="13" t="e">
+      <c r="T86" s="13" t="n">
         <f aca="false">MIN(197.4,(T85+S86))</f>
-        <v>#REF!</v>
+        <v>110.592222222222</v>
       </c>
       <c r="V86" s="8" t="n">
         <v>645.8</v>
@@ -7059,9 +7059,9 @@
         <f aca="false">J87-R87</f>
         <v>-1.05777777777778</v>
       </c>
-      <c r="T87" s="13" t="e">
+      <c r="T87" s="13" t="n">
         <f aca="false">MIN(197.4,(T86+S87))</f>
-        <v>#REF!</v>
+        <v>109.534444444445</v>
       </c>
       <c r="V87" s="8" t="n">
         <v>170.7</v>
@@ -7129,9 +7129,9 @@
         <f aca="false">J88-R88</f>
         <v>-0.313333333333333</v>
       </c>
-      <c r="T88" s="13" t="e">
+      <c r="T88" s="13" t="n">
         <f aca="false">MIN(197.4,(T87+S88))</f>
-        <v>#REF!</v>
+        <v>109.221111111111</v>
       </c>
       <c r="V88" s="8" t="n">
         <v>144.8</v>
@@ -7199,9 +7199,9 @@
         <f aca="false">J89-R89</f>
         <v>-0.843333333333334</v>
       </c>
-      <c r="T89" s="13" t="e">
+      <c r="T89" s="13" t="n">
         <f aca="false">MIN(197.4,(T88+S89))</f>
-        <v>#REF!</v>
+        <v>108.377777777778</v>
       </c>
       <c r="V89" s="8" t="n">
         <v>167.6</v>
@@ -7269,9 +7269,9 @@
         <f aca="false">J90-R90</f>
         <v>-0.295</v>
       </c>
-      <c r="T90" s="13" t="e">
+      <c r="T90" s="13" t="n">
         <f aca="false">MIN(197.4,(T89+S90))</f>
-        <v>#REF!</v>
+        <v>108.082777777778</v>
       </c>
       <c r="V90" s="8" t="n">
         <v>114.3</v>
@@ -7339,9 +7339,9 @@
         <f aca="false">J91-R91</f>
         <v>0.466666666666667</v>
       </c>
-      <c r="T91" s="13" t="e">
+      <c r="T91" s="13" t="n">
         <f aca="false">MIN(197.4,(T90+S91))</f>
-        <v>#REF!</v>
+        <v>108.549444444445</v>
       </c>
       <c r="V91" s="8" t="n">
         <v>285.7</v>
@@ -7409,9 +7409,9 @@
         <f aca="false">J92-R92</f>
         <v>-0.783333333333333</v>
       </c>
-      <c r="T92" s="13" t="e">
+      <c r="T92" s="13" t="n">
         <f aca="false">MIN(197.4,(T91+S92))</f>
-        <v>#REF!</v>
+        <v>107.766111111111</v>
       </c>
       <c r="V92" s="8" t="n">
         <v>629</v>
@@ -7479,9 +7479,9 @@
         <f aca="false">J93-R93</f>
         <v>-0.473333333333333</v>
       </c>
-      <c r="T93" s="13" t="e">
+      <c r="T93" s="13" t="n">
         <f aca="false">MIN(197.4,(T92+S93))</f>
-        <v>#REF!</v>
+        <v>107.292777777778</v>
       </c>
       <c r="V93" s="8" t="n">
         <v>115.6</v>
@@ -7549,9 +7549,9 @@
         <f aca="false">J94-R94</f>
         <v>1.08222222222222</v>
       </c>
-      <c r="T94" s="13" t="e">
+      <c r="T94" s="13" t="n">
         <f aca="false">MIN(197.4,(T93+S94))</f>
-        <v>#REF!</v>
+        <v>108.375</v>
       </c>
       <c r="V94" s="8" t="n">
         <v>96.4</v>
@@ -7619,9 +7619,9 @@
         <f aca="false">J95-R95</f>
         <v>2.4</v>
       </c>
-      <c r="T95" s="13" t="e">
+      <c r="T95" s="13" t="n">
         <f aca="false">MIN(197.4,(T94+S95))</f>
-        <v>#REF!</v>
+        <v>110.775</v>
       </c>
       <c r="V95" s="8" t="n">
         <v>607.1</v>
@@ -7689,9 +7689,9 @@
         <f aca="false">J96-R96</f>
         <v>1.61666666666667</v>
       </c>
-      <c r="T96" s="13" t="e">
+      <c r="T96" s="13" t="n">
         <f aca="false">MIN(197.4,(T95+S96))</f>
-        <v>#REF!</v>
+        <v>112.391666666667</v>
       </c>
       <c r="V96" s="8" t="n">
         <v>277</v>
@@ -7759,9 +7759,9 @@
         <f aca="false">J97-R97</f>
         <v>-0.367777777777778</v>
       </c>
-      <c r="T97" s="13" t="e">
+      <c r="T97" s="13" t="n">
         <f aca="false">MIN(197.4,(T96+S97))</f>
-        <v>#REF!</v>
+        <v>112.023888888889</v>
       </c>
       <c r="V97" s="8" t="n">
         <v>635.8</v>
@@ -7829,9 +7829,9 @@
         <f aca="false">J98-R98</f>
         <v>-0.49</v>
       </c>
-      <c r="T98" s="13" t="e">
+      <c r="T98" s="13" t="n">
         <f aca="false">MIN(197.4,(T97+S98))</f>
-        <v>#REF!</v>
+        <v>111.533888888889</v>
       </c>
       <c r="V98" s="8" t="n">
         <v>136.6</v>
@@ -7899,9 +7899,9 @@
         <f aca="false">J99-R99</f>
         <v>-0.328888888888889</v>
       </c>
-      <c r="T99" s="13" t="e">
+      <c r="T99" s="13" t="n">
         <f aca="false">MIN(197.4,(T98+S99))</f>
-        <v>#REF!</v>
+        <v>111.205</v>
       </c>
       <c r="V99" s="8" t="n">
         <v>194.6</v>
@@ -7969,9 +7969,9 @@
         <f aca="false">J100-R100</f>
         <v>-0.213888888888889</v>
       </c>
-      <c r="T100" s="13" t="e">
+      <c r="T100" s="13" t="n">
         <f aca="false">MIN(197.4,(T99+S100))</f>
-        <v>#REF!</v>
+        <v>110.991111111111</v>
       </c>
       <c r="V100" s="8" t="n">
         <v>215.2</v>
@@ -8039,9 +8039,9 @@
         <f aca="false">J101-R101</f>
         <v>-0.333333333333333</v>
       </c>
-      <c r="T101" s="13" t="e">
+      <c r="T101" s="13" t="n">
         <f aca="false">MIN(197.4,(T100+S101))</f>
-        <v>#REF!</v>
+        <v>110.657777777778</v>
       </c>
       <c r="V101" s="8" t="n">
         <v>162.2</v>
@@ -8109,9 +8109,9 @@
         <f aca="false">J102-R102</f>
         <v>1.09666666666667</v>
       </c>
-      <c r="T102" s="13" t="e">
+      <c r="T102" s="13" t="n">
         <f aca="false">MIN(197.4,(T101+S102))</f>
-        <v>#REF!</v>
+        <v>111.754444444445</v>
       </c>
       <c r="V102" s="8" t="n">
         <v>272.7</v>
@@ -8179,9 +8179,9 @@
         <f aca="false">J103-R103</f>
         <v>8.29333333333334</v>
       </c>
-      <c r="T103" s="13" t="e">
+      <c r="T103" s="13" t="n">
         <f aca="false">MIN(197.4,(T102+S103))</f>
-        <v>#REF!</v>
+        <v>120.047777777778</v>
       </c>
       <c r="V103" s="8" t="n">
         <v>84.4</v>
@@ -8249,9 +8249,9 @@
         <f aca="false">J104-R104</f>
         <v>0.09</v>
       </c>
-      <c r="T104" s="13" t="e">
+      <c r="T104" s="13" t="n">
         <f aca="false">MIN(197.4,(T103+S104))</f>
-        <v>#REF!</v>
+        <v>120.137777777778</v>
       </c>
       <c r="V104" s="8" t="n">
         <v>98.7</v>
@@ -8319,9 +8319,9 @@
         <f aca="false">J105-R105</f>
         <v>-0.498888888888889</v>
       </c>
-      <c r="T105" s="13" t="e">
+      <c r="T105" s="13" t="n">
         <f aca="false">MIN(197.4,(T104+S105))</f>
-        <v>#REF!</v>
+        <v>119.638888888889</v>
       </c>
       <c r="V105" s="8" t="n">
         <v>430.5</v>
@@ -8389,9 +8389,9 @@
         <f aca="false">J106-R106</f>
         <v>-0.258333333333333</v>
       </c>
-      <c r="T106" s="13" t="e">
+      <c r="T106" s="13" t="n">
         <f aca="false">MIN(197.4,(T105+S106))</f>
-        <v>#REF!</v>
+        <v>119.380555555556</v>
       </c>
       <c r="V106" s="8" t="n">
         <v>156.2</v>
@@ -8459,9 +8459,9 @@
         <f aca="false">J107-R107</f>
         <v>-1.38666666666667</v>
       </c>
-      <c r="T107" s="13" t="e">
+      <c r="T107" s="13" t="n">
         <f aca="false">MIN(197.4,(T106+S107))</f>
-        <v>#REF!</v>
+        <v>117.993888888889</v>
       </c>
       <c r="V107" s="8" t="n">
         <v>574.1</v>
@@ -8529,9 +8529,9 @@
         <f aca="false">J108-R108</f>
         <v>0.627777777777778</v>
       </c>
-      <c r="T108" s="13" t="e">
+      <c r="T108" s="13" t="n">
         <f aca="false">MIN(197.4,(T107+S108))</f>
-        <v>#REF!</v>
+        <v>118.621666666667</v>
       </c>
       <c r="V108" s="8" t="n">
         <v>158</v>
@@ -8599,9 +8599,9 @@
         <f aca="false">J109-R109</f>
         <v>0.797777777777778</v>
       </c>
-      <c r="T109" s="13" t="e">
+      <c r="T109" s="13" t="n">
         <f aca="false">MIN(197.4,(T108+S109))</f>
-        <v>#REF!</v>
+        <v>119.419444444445</v>
       </c>
       <c r="V109" s="8" t="n">
         <v>189.1</v>
@@ -8669,9 +8669,9 @@
         <f aca="false">J110-R110</f>
         <v>2.35833333333333</v>
       </c>
-      <c r="T110" s="13" t="e">
+      <c r="T110" s="13" t="n">
         <f aca="false">MIN(197.4,(T109+S110))</f>
-        <v>#REF!</v>
+        <v>121.777777777778</v>
       </c>
       <c r="V110" s="8" t="n">
         <v>91.8</v>
@@ -8739,9 +8739,9 @@
         <f aca="false">J111-R111</f>
         <v>-0.288888888888889</v>
       </c>
-      <c r="T111" s="13" t="e">
+      <c r="T111" s="13" t="n">
         <f aca="false">MIN(197.4,(T110+S111))</f>
-        <v>#REF!</v>
+        <v>121.488888888889</v>
       </c>
       <c r="V111" s="8" t="n">
         <v>562.3</v>
@@ -8809,9 +8809,9 @@
         <f aca="false">J112-R112</f>
         <v>3.86333333333333</v>
       </c>
-      <c r="T112" s="13" t="e">
+      <c r="T112" s="13" t="n">
         <f aca="false">MIN(197.4,(T111+S112))</f>
-        <v>#REF!</v>
+        <v>125.352222222222</v>
       </c>
       <c r="V112" s="8" t="n">
         <v>232.3</v>
@@ -8879,9 +8879,9 @@
         <f aca="false">J113-R113</f>
         <v>0.24</v>
       </c>
-      <c r="T113" s="13" t="e">
+      <c r="T113" s="13" t="n">
         <f aca="false">MIN(197.4,(T112+S113))</f>
-        <v>#REF!</v>
+        <v>125.592222222222</v>
       </c>
       <c r="V113" s="8" t="n">
         <v>181.7</v>
@@ -8949,9 +8949,9 @@
         <f aca="false">J114-R114</f>
         <v>-0.724444444444444</v>
       </c>
-      <c r="T114" s="13" t="e">
+      <c r="T114" s="13" t="n">
         <f aca="false">MIN(197.4,(T113+S114))</f>
-        <v>#REF!</v>
+        <v>124.867777777778</v>
       </c>
       <c r="V114" s="8" t="n">
         <v>581</v>
@@ -9019,9 +9019,9 @@
         <f aca="false">J115-R115</f>
         <v>-0.546666666666667</v>
       </c>
-      <c r="T115" s="13" t="e">
+      <c r="T115" s="13" t="n">
         <f aca="false">MIN(197.4,(T114+S115))</f>
-        <v>#REF!</v>
+        <v>124.321111111111</v>
       </c>
       <c r="V115" s="8" t="n">
         <v>232.1</v>
@@ -9089,9 +9089,9 @@
         <f aca="false">J116-R116</f>
         <v>0.0916666666666668</v>
       </c>
-      <c r="T116" s="13" t="e">
+      <c r="T116" s="13" t="n">
         <f aca="false">MIN(197.4,(T115+S116))</f>
-        <v>#REF!</v>
+        <v>124.412777777778</v>
       </c>
       <c r="V116" s="8" t="n">
         <v>502.9</v>
@@ -9159,9 +9159,9 @@
         <f aca="false">J117-R117</f>
         <v>-0.822222222222222</v>
       </c>
-      <c r="T117" s="13" t="e">
+      <c r="T117" s="13" t="n">
         <f aca="false">MIN(197.4,(T116+S117))</f>
-        <v>#REF!</v>
+        <v>123.590555555556</v>
       </c>
       <c r="V117" s="8" t="n">
         <v>562.9</v>
@@ -9229,9 +9229,9 @@
         <f aca="false">J118-R118</f>
         <v>1.32277777777778</v>
       </c>
-      <c r="T118" s="13" t="e">
+      <c r="T118" s="13" t="n">
         <f aca="false">MIN(197.4,(T117+S118))</f>
-        <v>#REF!</v>
+        <v>124.913333333333</v>
       </c>
       <c r="V118" s="8" t="n">
         <v>169.2</v>
@@ -9299,9 +9299,9 @@
         <f aca="false">J119-R119</f>
         <v>1.16666666666667</v>
       </c>
-      <c r="T119" s="13" t="e">
+      <c r="T119" s="13" t="n">
         <f aca="false">MIN(197.4,(T118+S119))</f>
-        <v>#REF!</v>
+        <v>126.08</v>
       </c>
       <c r="V119" s="8" t="n">
         <v>552.9</v>
@@ -9369,9 +9369,9 @@
         <f aca="false">J120-R120</f>
         <v>0.236666666666667</v>
       </c>
-      <c r="T120" s="13" t="e">
+      <c r="T120" s="13" t="n">
         <f aca="false">MIN(197.4,(T119+S120))</f>
-        <v>#REF!</v>
+        <v>126.316666666667</v>
       </c>
       <c r="V120" s="8" t="n">
         <v>178.1</v>
@@ -9439,9 +9439,9 @@
         <f aca="false">J121-R121</f>
         <v>1.36111111111111</v>
       </c>
-      <c r="T121" s="13" t="e">
+      <c r="T121" s="13" t="n">
         <f aca="false">MIN(197.4,(T120+S121))</f>
-        <v>#REF!</v>
+        <v>127.677777777778</v>
       </c>
       <c r="V121" s="8" t="n">
         <v>165.3</v>
@@ -9509,9 +9509,9 @@
         <f aca="false">J122-R122</f>
         <v>10.82</v>
       </c>
-      <c r="T122" s="13" t="e">
+      <c r="T122" s="13" t="n">
         <f aca="false">MIN(197.4,(T121+S122))</f>
-        <v>#REF!</v>
+        <v>138.497777777778</v>
       </c>
       <c r="V122" s="8" t="n">
         <v>75.2</v>
@@ -9579,9 +9579,9 @@
         <f aca="false">J123-R123</f>
         <v>-0.746666666666667</v>
       </c>
-      <c r="T123" s="13" t="e">
+      <c r="T123" s="13" t="n">
         <f aca="false">MIN(197.4,(T122+S123))</f>
-        <v>#REF!</v>
+        <v>137.751111111111</v>
       </c>
       <c r="V123" s="8" t="n">
         <v>230.4</v>
@@ -9649,9 +9649,9 @@
         <f aca="false">J124-R124</f>
         <v>-0.568888888888889</v>
       </c>
-      <c r="T124" s="13" t="e">
+      <c r="T124" s="13" t="n">
         <f aca="false">MIN(197.4,(T123+S124))</f>
-        <v>#REF!</v>
+        <v>137.182222222222</v>
       </c>
       <c r="V124" s="8" t="n">
         <v>414</v>
@@ -9719,9 +9719,9 @@
         <f aca="false">J125-R125</f>
         <v>12.4366666666667</v>
       </c>
-      <c r="T125" s="13" t="e">
+      <c r="T125" s="13" t="n">
         <f aca="false">MIN(197.4,(T124+S125))</f>
-        <v>#REF!</v>
+        <v>149.618888888889</v>
       </c>
       <c r="V125" s="8" t="n">
         <v>489.8</v>
@@ -9789,9 +9789,9 @@
         <f aca="false">J126-R126</f>
         <v>-0.869444444444445</v>
       </c>
-      <c r="T126" s="13" t="e">
+      <c r="T126" s="13" t="n">
         <f aca="false">MIN(197.4,(T125+S126))</f>
-        <v>#REF!</v>
+        <v>148.749444444445</v>
       </c>
       <c r="V126" s="8" t="n">
         <v>255.6</v>
@@ -9859,9 +9859,9 @@
         <f aca="false">J127-R127</f>
         <v>5.30222222222222</v>
       </c>
-      <c r="T127" s="13" t="e">
+      <c r="T127" s="13" t="n">
         <f aca="false">MIN(197.4,(T126+S127))</f>
-        <v>#REF!</v>
+        <v>154.051666666667</v>
       </c>
       <c r="V127" s="8" t="n">
         <v>95.2</v>
@@ -9929,9 +9929,9 @@
         <f aca="false">J128-R128</f>
         <v>4.71666666666667</v>
       </c>
-      <c r="T128" s="13" t="e">
+      <c r="T128" s="13" t="n">
         <f aca="false">MIN(197.4,(T127+S128))</f>
-        <v>#REF!</v>
+        <v>158.768333333333</v>
       </c>
       <c r="V128" s="8" t="n">
         <v>154.2</v>
@@ -9999,9 +9999,9 @@
         <f aca="false">J129-R129</f>
         <v>8.50666666666667</v>
       </c>
-      <c r="T129" s="13" t="e">
+      <c r="T129" s="13" t="n">
         <f aca="false">MIN(197.4,(T128+S129))</f>
-        <v>#REF!</v>
+        <v>167.275</v>
       </c>
       <c r="V129" s="8" t="n">
         <v>254.8</v>
@@ -10069,9 +10069,9 @@
         <f aca="false">J130-R130</f>
         <v>3.005</v>
       </c>
-      <c r="T130" s="13" t="e">
+      <c r="T130" s="13" t="n">
         <f aca="false">MIN(197.4,(T129+S130))</f>
-        <v>#REF!</v>
+        <v>170.28</v>
       </c>
       <c r="V130" s="8" t="n">
         <v>379.1</v>
@@ -10139,9 +10139,9 @@
         <f aca="false">J131-R131</f>
         <v>-1.2</v>
       </c>
-      <c r="T131" s="21" t="e">
+      <c r="T131" s="21" t="n">
         <f aca="false">MIN(197.4,(T130+S131))</f>
-        <v>#REF!</v>
+        <v>169.08</v>
       </c>
       <c r="V131" s="18" t="n">
         <v>341</v>
@@ -10216,9 +10216,9 @@
         <f aca="false">J132-R132</f>
         <v>1.9</v>
       </c>
-      <c r="T132" s="13" t="e">
+      <c r="T132" s="13" t="n">
         <f aca="false">MIN(197.4,(T131+S132))</f>
-        <v>#REF!</v>
+        <v>170.98</v>
       </c>
       <c r="U132" s="26" t="s">
         <v>29</v>
@@ -10303,9 +10303,9 @@
         <f aca="false">J133-R133</f>
         <v>0.7</v>
       </c>
-      <c r="T133" s="13" t="e">
+      <c r="T133" s="13" t="n">
         <f aca="false">MIN(197.4,(T132+S133))</f>
-        <v>#REF!</v>
+        <v>171.68</v>
       </c>
       <c r="U133" s="8" t="n">
         <v>3</v>
@@ -10389,9 +10389,9 @@
         <f aca="false">J134-R134</f>
         <v>2.1</v>
       </c>
-      <c r="T134" s="13" t="e">
+      <c r="T134" s="13" t="n">
         <f aca="false">MIN(197.4,(T133+S134))</f>
-        <v>#REF!</v>
+        <v>173.78</v>
       </c>
       <c r="U134" s="26" t="s">
         <v>32</v>
@@ -10476,9 +10476,9 @@
         <f aca="false">J135-R135</f>
         <v>0.2</v>
       </c>
-      <c r="T135" s="13" t="e">
+      <c r="T135" s="13" t="n">
         <f aca="false">MIN(197.4,(T134+S135))</f>
-        <v>#REF!</v>
+        <v>173.98</v>
       </c>
       <c r="U135" s="8" t="n">
         <v>0</v>
@@ -10563,9 +10563,9 @@
         <f aca="false">J136-R136</f>
         <v>4.4</v>
       </c>
-      <c r="T136" s="13" t="e">
+      <c r="T136" s="13" t="n">
         <f aca="false">MIN(197.4,(T135+S136))</f>
-        <v>#REF!</v>
+        <v>178.38</v>
       </c>
       <c r="U136" s="26" t="s">
         <v>35</v>
@@ -10650,9 +10650,9 @@
         <f aca="false">J137-R137</f>
         <v>2.2</v>
       </c>
-      <c r="T137" s="13" t="e">
+      <c r="T137" s="13" t="n">
         <f aca="false">MIN(197.4,(T136+S137))</f>
-        <v>#REF!</v>
+        <v>180.58</v>
       </c>
       <c r="U137" s="8" t="n">
         <v>0</v>
@@ -10736,9 +10736,9 @@
         <f aca="false">J138-R138</f>
         <v>-0.3</v>
       </c>
-      <c r="T138" s="13" t="e">
+      <c r="T138" s="13" t="n">
         <f aca="false">MIN(197.4,(T137+S138))</f>
-        <v>#REF!</v>
+        <v>180.28</v>
       </c>
       <c r="U138" s="26" t="s">
         <v>38</v>
@@ -10819,13 +10819,13 @@
         <f aca="false">J139-R139</f>
         <v>-0.4</v>
       </c>
-      <c r="T139" s="13" t="e">
+      <c r="T139" s="13" t="n">
         <f aca="false">MIN(197.4,(T138+S139))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U139" s="13" t="e">
+        <v>179.88</v>
+      </c>
+      <c r="U139" s="13" t="n">
         <f aca="false">MIN(T132:T143)</f>
-        <v>#REF!</v>
+        <v>170.98</v>
       </c>
       <c r="V139" s="8" t="n">
         <v>154.2</v>
@@ -10903,9 +10903,9 @@
         <f aca="false">J140-R140</f>
         <v>3.6</v>
       </c>
-      <c r="T140" s="13" t="e">
+      <c r="T140" s="13" t="n">
         <f aca="false">MIN(197.4,(T139+S140))</f>
-        <v>#REF!</v>
+        <v>183.48</v>
       </c>
       <c r="U140" s="26" t="s">
         <v>40</v>
@@ -10986,13 +10986,13 @@
         <f aca="false">J141-R141</f>
         <v>4.3</v>
       </c>
-      <c r="T141" s="13" t="e">
+      <c r="T141" s="13" t="n">
         <f aca="false">MIN(197.4,(T140+S141))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U141" s="13" t="e">
+        <v>187.78</v>
+      </c>
+      <c r="U141" s="13" t="n">
         <f aca="false">MAX(T132:T143)</f>
-        <v>#REF!</v>
+        <v>188.18</v>
       </c>
       <c r="V141" s="8" t="n">
         <v>120.1</v>
@@ -11070,9 +11070,9 @@
         <f aca="false">J142-R142</f>
         <v>0.4</v>
       </c>
-      <c r="T142" s="13" t="e">
+      <c r="T142" s="13" t="n">
         <f aca="false">MIN(197.4,(T141+S142))</f>
-        <v>#REF!</v>
+        <v>188.18</v>
       </c>
       <c r="U142" s="26" t="s">
         <v>42</v>
@@ -11153,13 +11153,13 @@
         <f aca="false">J143-R143</f>
         <v>-0.9</v>
       </c>
-      <c r="T143" s="21" t="e">
+      <c r="T143" s="21" t="n">
         <f aca="false">MIN(197.4,(T142+S143))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U143" s="29" t="e">
+        <v>187.28</v>
+      </c>
+      <c r="U143" s="29" t="n">
         <f aca="false">AVERAGE(T132:T143)</f>
-        <v>#REF!</v>
+        <v>179.688333333333</v>
       </c>
       <c r="V143" s="18" t="n">
         <v>527.9</v>
@@ -11239,9 +11239,9 @@
         <f aca="false">J144-R144</f>
         <v>-0.301052631578947</v>
       </c>
-      <c r="T144" s="13" t="e">
+      <c r="T144" s="13" t="n">
         <f aca="false">MIN(197.4,(T143+S144))</f>
-        <v>#REF!</v>
+        <v>186.978947368421</v>
       </c>
       <c r="U144" s="26" t="s">
         <v>46</v>
@@ -11322,9 +11322,9 @@
         <f aca="false">J145-R145</f>
         <v>-0.00315789473684214</v>
       </c>
-      <c r="T145" s="13" t="e">
+      <c r="T145" s="13" t="n">
         <f aca="false">MIN(197.4,(T144+S145))</f>
-        <v>#REF!</v>
+        <v>186.975789473684</v>
       </c>
       <c r="U145" s="13" t="n">
         <v>9</v>
@@ -11403,9 +11403,9 @@
         <f aca="false">J146-R146</f>
         <v>14.5944736842105</v>
       </c>
-      <c r="T146" s="13" t="e">
+      <c r="T146" s="13" t="n">
         <f aca="false">MIN(197.4,(T145+S146))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V146" s="8" t="n">
         <v>84.5</v>
@@ -11481,13 +11481,13 @@
         <f aca="false">J147-R147</f>
         <v>-0.306315789473684</v>
       </c>
-      <c r="T147" s="13" t="e">
+      <c r="T147" s="13" t="n">
         <f aca="false">MIN(197.4,(T146+S147))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U147" s="13" t="e">
+        <v>197.093684210526</v>
+      </c>
+      <c r="U147" s="13" t="n">
         <f aca="false">(U143*100)/197.4</f>
-        <v>#REF!</v>
+        <v>91.0275244849713</v>
       </c>
       <c r="V147" s="8" t="n">
         <v>434</v>
@@ -11563,9 +11563,9 @@
         <f aca="false">J148-R148</f>
         <v>0.497368421052632</v>
       </c>
-      <c r="T148" s="13" t="e">
+      <c r="T148" s="13" t="n">
         <f aca="false">MIN(197.4,(T147+S148))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V148" s="8" t="n">
         <v>148.5</v>
@@ -11644,9 +11644,9 @@
         <f aca="false">J149-R149</f>
         <v>8.69052631578948</v>
       </c>
-      <c r="T149" s="13" t="e">
+      <c r="T149" s="13" t="n">
         <f aca="false">MIN(197.4,(T148+S149))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="U149" s="32" t="s">
         <v>29</v>
@@ -11732,9 +11732,9 @@
         <f aca="false">J150-R150</f>
         <v>-0.105526315789474</v>
       </c>
-      <c r="T150" s="13" t="e">
+      <c r="T150" s="13" t="n">
         <f aca="false">MIN(197.4,(T149+S150))</f>
-        <v>#REF!</v>
+        <v>197.294473684211</v>
       </c>
       <c r="U150" s="8" t="n">
         <v>31</v>
@@ -11819,9 +11819,9 @@
         <f aca="false">J151-R151</f>
         <v>-0.921052631578948</v>
       </c>
-      <c r="T151" s="13" t="e">
+      <c r="T151" s="13" t="n">
         <f aca="false">MIN(197.4,(T150+S151))</f>
-        <v>#REF!</v>
+        <v>196.373421052632</v>
       </c>
       <c r="U151" s="32" t="s">
         <v>32</v>
@@ -11907,9 +11907,9 @@
         <f aca="false">J152-R152</f>
         <v>3.58815789473684</v>
       </c>
-      <c r="T152" s="13" t="e">
+      <c r="T152" s="13" t="n">
         <f aca="false">MIN(197.4,(T151+S152))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="U152" s="8" t="n">
         <v>0</v>
@@ -11995,9 +11995,9 @@
         <f aca="false">J153-R153</f>
         <v>-1.23684210526316</v>
       </c>
-      <c r="T153" s="13" t="e">
+      <c r="T153" s="13" t="n">
         <f aca="false">MIN(197.4,(T152+S153))</f>
-        <v>#REF!</v>
+        <v>196.163157894737</v>
       </c>
       <c r="U153" s="32" t="s">
         <v>35</v>
@@ -12083,9 +12083,9 @@
         <f aca="false">J154-R154</f>
         <v>0.1</v>
       </c>
-      <c r="T154" s="13" t="e">
+      <c r="T154" s="13" t="n">
         <f aca="false">MIN(197.4,(T153+S154))</f>
-        <v>#REF!</v>
+        <v>196.263157894737</v>
       </c>
       <c r="U154" s="8" t="n">
         <v>0</v>
@@ -12170,9 +12170,9 @@
         <f aca="false">J155-R155</f>
         <v>-0.415789473684211</v>
       </c>
-      <c r="T155" s="13" t="e">
+      <c r="T155" s="13" t="n">
         <f aca="false">MIN(197.4,(T154+S155))</f>
-        <v>#REF!</v>
+        <v>195.847368421053</v>
       </c>
       <c r="U155" s="32" t="s">
         <v>38</v>
@@ -12254,13 +12254,13 @@
         <f aca="false">J156-R156</f>
         <v>3.94526315789474</v>
       </c>
-      <c r="T156" s="13" t="e">
+      <c r="T156" s="13" t="n">
         <f aca="false">MIN(197.4,(T155+S156))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U156" s="13" t="e">
+        <v>197.4</v>
+      </c>
+      <c r="U156" s="13" t="n">
         <f aca="false">MIN(T144:T200)</f>
-        <v>#REF!</v>
+        <v>175.653947368421</v>
       </c>
       <c r="V156" s="8" t="n">
         <v>226.1</v>
@@ -12339,9 +12339,9 @@
         <f aca="false">J157-R157</f>
         <v>1.15210526315789</v>
       </c>
-      <c r="T157" s="13" t="e">
+      <c r="T157" s="13" t="n">
         <f aca="false">MIN(197.4,(T156+S157))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="U157" s="32" t="s">
         <v>40</v>
@@ -12423,13 +12423,13 @@
         <f aca="false">J158-R158</f>
         <v>5.4171052631579</v>
       </c>
-      <c r="T158" s="13" t="e">
+      <c r="T158" s="13" t="n">
         <f aca="false">MIN(197.4,(T157+S158))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U158" s="13" t="e">
+        <v>197.4</v>
+      </c>
+      <c r="U158" s="13" t="n">
         <f aca="false">MAX(T144:T200)</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V158" s="8" t="n">
         <v>347.3</v>
@@ -12508,9 +12508,9 @@
         <f aca="false">J159-R159</f>
         <v>2.6621052631579</v>
       </c>
-      <c r="T159" s="13" t="e">
+      <c r="T159" s="13" t="n">
         <f aca="false">MIN(197.4,(T158+S159))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="U159" s="32" t="s">
         <v>42</v>
@@ -12592,13 +12592,13 @@
         <f aca="false">J160-R160</f>
         <v>-1.25368421052632</v>
       </c>
-      <c r="T160" s="13" t="e">
+      <c r="T160" s="13" t="n">
         <f aca="false">MIN(197.4,(T159+S160))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U160" s="14" t="e">
+        <v>196.146315789474</v>
+      </c>
+      <c r="U160" s="14" t="n">
         <f aca="false">AVERAGE(T144:T200)</f>
-        <v>#REF!</v>
+        <v>194.04190212373</v>
       </c>
       <c r="V160" s="8" t="n">
         <v>943.7</v>
@@ -12677,9 +12677,9 @@
         <f aca="false">J161-R161</f>
         <v>4.6621052631579</v>
       </c>
-      <c r="T161" s="13" t="e">
+      <c r="T161" s="13" t="n">
         <f aca="false">MIN(197.4,(T160+S161))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V161" s="8" t="n">
         <v>782.1</v>
@@ -12758,13 +12758,13 @@
         <f aca="false">J162-R162</f>
         <v>6.67</v>
       </c>
-      <c r="T162" s="13" t="e">
+      <c r="T162" s="13" t="n">
         <f aca="false">MIN(197.4,(T161+S162))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U162" s="13" t="e">
+        <v>197.4</v>
+      </c>
+      <c r="U162" s="13" t="n">
         <f aca="false">(U160*100)/197.4</f>
-        <v>#REF!</v>
+        <v>98.2988359289414</v>
       </c>
       <c r="V162" s="8" t="n">
         <v>147.9</v>
@@ -12842,9 +12842,9 @@
         <f aca="false">J163-R163</f>
         <v>0.963157894736842</v>
       </c>
-      <c r="T163" s="13" t="e">
+      <c r="T163" s="13" t="n">
         <f aca="false">MIN(197.4,(T162+S163))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V163" s="8" t="n">
         <v>252.2</v>
@@ -12920,9 +12920,9 @@
         <f aca="false">J164-R164</f>
         <v>0.0447368421052632</v>
       </c>
-      <c r="T164" s="13" t="e">
+      <c r="T164" s="13" t="n">
         <f aca="false">MIN(197.4,(T163+S164))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V164" s="8" t="n">
         <v>621.2</v>
@@ -12998,9 +12998,9 @@
         <f aca="false">J165-R165</f>
         <v>-1.48105263157895</v>
       </c>
-      <c r="T165" s="13" t="e">
+      <c r="T165" s="13" t="n">
         <f aca="false">MIN(197.4,(T164+S165))</f>
-        <v>#REF!</v>
+        <v>195.918947368421</v>
       </c>
       <c r="V165" s="8" t="n">
         <v>765.9</v>
@@ -13076,9 +13076,9 @@
         <f aca="false">J166-R166</f>
         <v>-0.954473684210526</v>
       </c>
-      <c r="T166" s="13" t="e">
+      <c r="T166" s="13" t="n">
         <f aca="false">MIN(197.4,(T165+S166))</f>
-        <v>#REF!</v>
+        <v>194.964473684211</v>
       </c>
       <c r="V166" s="8" t="n">
         <v>663.4</v>
@@ -13154,9 +13154,9 @@
         <f aca="false">J167-R167</f>
         <v>5.84947368421053</v>
       </c>
-      <c r="T167" s="13" t="e">
+      <c r="T167" s="13" t="n">
         <f aca="false">MIN(197.4,(T166+S167))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V167" s="8" t="n">
         <v>429.1</v>
@@ -13232,9 +13232,9 @@
         <f aca="false">J168-R168</f>
         <v>-0.0460526315789472</v>
       </c>
-      <c r="T168" s="13" t="e">
+      <c r="T168" s="13" t="n">
         <f aca="false">MIN(197.4,(T167+S168))</f>
-        <v>#REF!</v>
+        <v>197.353947368421</v>
       </c>
       <c r="V168" s="8" t="n">
         <v>608.5</v>
@@ -13310,9 +13310,9 @@
         <f aca="false">J169-R169</f>
         <v>0.145263157894737</v>
       </c>
-      <c r="T169" s="13" t="e">
+      <c r="T169" s="13" t="n">
         <f aca="false">MIN(197.4,(T168+S169))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V169" s="8" t="n">
         <v>880.3</v>
@@ -13393,9 +13393,9 @@
         <f aca="false">J170-R170</f>
         <v>-0.128421052631579</v>
       </c>
-      <c r="T170" s="13" t="e">
+      <c r="T170" s="13" t="n">
         <f aca="false">MIN(197.4,(T169+S170))</f>
-        <v>#REF!</v>
+        <v>197.271578947368</v>
       </c>
       <c r="V170" s="8" t="n">
         <v>251.8</v>
@@ -13411,9 +13411,9 @@
       <c r="AA170" s="8" t="n">
         <v>10.4703970378929</v>
       </c>
-      <c r="AB170" s="14" t="e">
+      <c r="AB170" s="14" t="n">
         <f aca="false">AVERAGE(T176:T189)</f>
-        <v>#REF!</v>
+        <v>195.185357142857</v>
       </c>
     </row>
     <row r="171" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13475,9 +13475,9 @@
         <f aca="false">J171-R171</f>
         <v>-0.751578947368421</v>
       </c>
-      <c r="T171" s="13" t="e">
+      <c r="T171" s="13" t="n">
         <f aca="false">MIN(197.4,(T170+S171))</f>
-        <v>#REF!</v>
+        <v>196.52</v>
       </c>
       <c r="V171" s="8" t="n">
         <v>181.9</v>
@@ -13556,9 +13556,9 @@
         <f aca="false">J172-R172</f>
         <v>2.83894736842105</v>
       </c>
-      <c r="T172" s="13" t="e">
+      <c r="T172" s="13" t="n">
         <f aca="false">MIN(197.4,(T171+S172))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V172" s="8" t="n">
         <v>184.3</v>
@@ -13637,9 +13637,9 @@
         <f aca="false">J173-R173</f>
         <v>1.43684210526316</v>
       </c>
-      <c r="T173" s="13" t="e">
+      <c r="T173" s="13" t="n">
         <f aca="false">MIN(197.4,(T172+S173))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V173" s="8" t="n">
         <v>280.1</v>
@@ -13718,9 +13718,9 @@
         <f aca="false">J174-R174</f>
         <v>10.5510526315789</v>
       </c>
-      <c r="T174" s="13" t="e">
+      <c r="T174" s="13" t="n">
         <f aca="false">MIN(197.4,(T173+S174))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V174" s="8" t="n">
         <v>175.9</v>
@@ -13799,9 +13799,9 @@
         <f aca="false">J175-R175</f>
         <v>-0.775789473684211</v>
       </c>
-      <c r="T175" s="13" t="e">
+      <c r="T175" s="13" t="n">
         <f aca="false">MIN(197.4,(T174+S175))</f>
-        <v>#REF!</v>
+        <v>196.624210526316</v>
       </c>
       <c r="V175" s="8" t="n">
         <v>586.7</v>
@@ -13880,9 +13880,9 @@
         <f aca="false">J176-R176</f>
         <v>-1.52157894736842</v>
       </c>
-      <c r="T176" s="35" t="e">
+      <c r="T176" s="35" t="n">
         <f aca="false">MIN(197.4,(T175+S176))</f>
-        <v>#REF!</v>
+        <v>195.102631578947</v>
       </c>
       <c r="V176" s="8" t="n">
         <v>930</v>
@@ -13963,9 +13963,9 @@
         <f aca="false">J177-R177</f>
         <v>-2.17894736842105</v>
       </c>
-      <c r="T177" s="35" t="e">
+      <c r="T177" s="35" t="n">
         <f aca="false">MIN(197.4,(T176+S177))</f>
-        <v>#REF!</v>
+        <v>192.923684210526</v>
       </c>
       <c r="V177" s="8" t="n">
         <v>1042.6</v>
@@ -14044,9 +14044,9 @@
         <f aca="false">J178-R178</f>
         <v>-2.18421052631579</v>
       </c>
-      <c r="T178" s="35" t="e">
+      <c r="T178" s="35" t="n">
         <f aca="false">MIN(197.4,(T177+S178))</f>
-        <v>#REF!</v>
+        <v>190.739473684211</v>
       </c>
       <c r="V178" s="8" t="n">
         <v>1171.4</v>
@@ -14128,9 +14128,9 @@
         <f aca="false">J179-R179</f>
         <v>-1.97052631578947</v>
       </c>
-      <c r="T179" s="40" t="e">
+      <c r="T179" s="40" t="n">
         <f aca="false">MIN(197.4,(T178+S179))</f>
-        <v>#REF!</v>
+        <v>188.768947368421</v>
       </c>
       <c r="V179" s="38" t="n">
         <v>1398.9</v>
@@ -14206,9 +14206,9 @@
         <f aca="false">J180-R180</f>
         <v>2.86105263157895</v>
       </c>
-      <c r="T180" s="35" t="e">
+      <c r="T180" s="35" t="n">
         <f aca="false">MIN(197.4,(T179+S180))</f>
-        <v>#REF!</v>
+        <v>191.63</v>
       </c>
       <c r="V180" s="8" t="n">
         <v>363.6</v>
@@ -14284,9 +14284,9 @@
         <f aca="false">J181-R181</f>
         <v>4.89</v>
       </c>
-      <c r="T181" s="35" t="e">
+      <c r="T181" s="35" t="n">
         <f aca="false">MIN(197.4,(T180+S181))</f>
-        <v>#REF!</v>
+        <v>196.52</v>
       </c>
       <c r="V181" s="8" t="n">
         <v>659.4</v>
@@ -14362,9 +14362,9 @@
         <f aca="false">J182-R182</f>
         <v>5.12815789473684</v>
       </c>
-      <c r="T182" s="35" t="e">
+      <c r="T182" s="35" t="n">
         <f aca="false">MIN(197.4,(T181+S182))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V182" s="8" t="n">
         <v>334.5</v>
@@ -14439,9 +14439,9 @@
         <f aca="false">J183-R183</f>
         <v>5.54736842105263</v>
       </c>
-      <c r="T183" s="35" t="e">
+      <c r="T183" s="35" t="n">
         <f aca="false">MIN(197.4,(T182+S183))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V183" s="8" t="n">
         <v>254.3</v>
@@ -14518,9 +14518,9 @@
         <f aca="false">J184-R184</f>
         <v>0.692105263157895</v>
       </c>
-      <c r="T184" s="35" t="e">
+      <c r="T184" s="35" t="n">
         <f aca="false">MIN(197.4,(T183+S184))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V184" s="8" t="n">
         <v>530.6</v>
@@ -14596,9 +14596,9 @@
         <f aca="false">J185-R185</f>
         <v>-0.632631578947368</v>
       </c>
-      <c r="T185" s="35" t="e">
+      <c r="T185" s="35" t="n">
         <f aca="false">MIN(197.4,(T184+S185))</f>
-        <v>#REF!</v>
+        <v>196.767368421053</v>
       </c>
       <c r="V185" s="8" t="n">
         <v>1089.9</v>
@@ -14674,9 +14674,9 @@
         <f aca="false">J186-R186</f>
         <v>-1.02447368421053</v>
       </c>
-      <c r="T186" s="35" t="e">
+      <c r="T186" s="35" t="n">
         <f aca="false">MIN(197.4,(T185+S186))</f>
-        <v>#REF!</v>
+        <v>195.742894736842</v>
       </c>
       <c r="V186" s="8" t="n">
         <v>732.3</v>
@@ -14751,9 +14751,9 @@
         <f aca="false">J187-R187</f>
         <v>10.5768421052632</v>
       </c>
-      <c r="T187" s="35" t="e">
+      <c r="T187" s="35" t="n">
         <f aca="false">MIN(197.4,(T186+S187))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V187" s="8" t="n">
         <v>264.3</v>
@@ -14828,9 +14828,9 @@
         <f aca="false">J188-R188</f>
         <v>14.0934210526316</v>
       </c>
-      <c r="T188" s="35" t="e">
+      <c r="T188" s="35" t="n">
         <f aca="false">MIN(197.4,(T187+S188))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V188" s="8" t="n">
         <v>249.3</v>
@@ -14905,9 +14905,9 @@
         <f aca="false">J189-R189</f>
         <v>0.103157894736842</v>
       </c>
-      <c r="T189" s="35" t="e">
+      <c r="T189" s="35" t="n">
         <f aca="false">MIN(197.4,(T188+S189))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V189" s="8" t="n">
         <v>247.2</v>
@@ -14983,9 +14983,9 @@
         <f aca="false">J190-R190</f>
         <v>-0.911315789473684</v>
       </c>
-      <c r="T190" s="13" t="e">
+      <c r="T190" s="13" t="n">
         <f aca="false">MIN(197.4,(T189+S190))</f>
-        <v>#REF!</v>
+        <v>196.488684210526</v>
       </c>
       <c r="V190" s="8" t="n">
         <v>554.8</v>
@@ -15063,9 +15063,9 @@
         <f aca="false">J191-R191</f>
         <v>-1.68947368421053</v>
       </c>
-      <c r="T191" s="13" t="e">
+      <c r="T191" s="13" t="n">
         <f aca="false">MIN(197.4,(T190+S191))</f>
-        <v>#REF!</v>
+        <v>194.799210526316</v>
       </c>
       <c r="V191" s="8" t="n">
         <v>1405.6</v>
@@ -15141,9 +15141,9 @@
         <f aca="false">J192-R192</f>
         <v>-2.03210526315789</v>
       </c>
-      <c r="T192" s="13" t="e">
+      <c r="T192" s="13" t="n">
         <f aca="false">MIN(197.4,(T191+S192))</f>
-        <v>#REF!</v>
+        <v>192.767105263158</v>
       </c>
       <c r="V192" s="8" t="n">
         <v>1596.3</v>
@@ -15219,9 +15219,9 @@
         <f aca="false">J193-R193</f>
         <v>-2.38947368421053</v>
       </c>
-      <c r="T193" s="13" t="e">
+      <c r="T193" s="13" t="n">
         <f aca="false">MIN(197.4,(T192+S193))</f>
-        <v>#REF!</v>
+        <v>190.377631578947</v>
       </c>
       <c r="V193" s="8" t="n">
         <v>1473.5</v>
@@ -15297,9 +15297,9 @@
         <f aca="false">J194-R194</f>
         <v>-2.26842105263158</v>
       </c>
-      <c r="T194" s="13" t="e">
+      <c r="T194" s="13" t="n">
         <f aca="false">MIN(197.4,(T193+S194))</f>
-        <v>#REF!</v>
+        <v>188.109210526316</v>
       </c>
       <c r="V194" s="8" t="n">
         <v>1718</v>
@@ -15375,9 +15375,9 @@
         <f aca="false">J195-R195</f>
         <v>-2.50105263157895</v>
       </c>
-      <c r="T195" s="13" t="e">
+      <c r="T195" s="13" t="n">
         <f aca="false">MIN(197.4,(T194+S195))</f>
-        <v>#REF!</v>
+        <v>185.608157894737</v>
       </c>
       <c r="V195" s="8" t="n">
         <v>1045.1</v>
@@ -15453,9 +15453,9 @@
         <f aca="false">J196-R196</f>
         <v>-2.62078947368421</v>
       </c>
-      <c r="T196" s="13" t="e">
+      <c r="T196" s="13" t="n">
         <f aca="false">MIN(197.4,(T195+S196))</f>
-        <v>#REF!</v>
+        <v>182.987368421053</v>
       </c>
       <c r="V196" s="8" t="n">
         <v>1648.5</v>
@@ -15531,9 +15531,9 @@
         <f aca="false">J197-R197</f>
         <v>-2.39842105263158</v>
       </c>
-      <c r="T197" s="13" t="e">
+      <c r="T197" s="13" t="n">
         <f aca="false">MIN(197.4,(T196+S197))</f>
-        <v>#REF!</v>
+        <v>180.588947368421</v>
       </c>
       <c r="V197" s="8" t="n">
         <v>1652.5</v>
@@ -15611,9 +15611,9 @@
         <f aca="false">J198-R198</f>
         <v>-1.25921052631579</v>
       </c>
-      <c r="T198" s="13" t="e">
+      <c r="T198" s="13" t="n">
         <f aca="false">MIN(197.4,(T197+S198))</f>
-        <v>#REF!</v>
+        <v>179.329736842105</v>
       </c>
       <c r="V198" s="8" t="n">
         <v>918.6</v>
@@ -15689,9 +15689,9 @@
         <f aca="false">J199-R199</f>
         <v>-1.83578947368421</v>
       </c>
-      <c r="T199" s="13" t="e">
+      <c r="T199" s="13" t="n">
         <f aca="false">MIN(197.4,(T198+S199))</f>
-        <v>#REF!</v>
+        <v>177.493947368421</v>
       </c>
       <c r="V199" s="8" t="n">
         <v>748.7</v>
@@ -15767,9 +15767,9 @@
         <f aca="false">J200-R200</f>
         <v>-1.84</v>
       </c>
-      <c r="T200" s="21" t="e">
+      <c r="T200" s="21" t="n">
         <f aca="false">MIN(197.4,(T199+S200))</f>
-        <v>#REF!</v>
+        <v>175.653947368421</v>
       </c>
       <c r="V200" s="18" t="n">
         <v>469.4</v>
@@ -15847,9 +15847,9 @@
         <f aca="false">J201-R201</f>
         <v>-2.07</v>
       </c>
-      <c r="T201" s="13" t="e">
+      <c r="T201" s="13" t="n">
         <f aca="false">MIN(197.4,(T200+S201))</f>
-        <v>#REF!</v>
+        <v>173.583947368421</v>
       </c>
       <c r="U201" s="45" t="s">
         <v>29</v>
@@ -15932,9 +15932,9 @@
         <f aca="false">J202-R202</f>
         <v>-2.3</v>
       </c>
-      <c r="T202" s="13" t="e">
+      <c r="T202" s="13" t="n">
         <f aca="false">MIN(197.4,(T201+S202))</f>
-        <v>#REF!</v>
+        <v>171.283947368421</v>
       </c>
       <c r="U202" s="8" t="n">
         <v>14</v>
@@ -16017,9 +16017,9 @@
         <f aca="false">J203-R203</f>
         <v>3.28</v>
       </c>
-      <c r="T203" s="13" t="e">
+      <c r="T203" s="13" t="n">
         <f aca="false">MIN(197.4,(T202+S203))</f>
-        <v>#REF!</v>
+        <v>174.563947368421</v>
       </c>
       <c r="U203" s="45" t="s">
         <v>32</v>
@@ -16103,9 +16103,9 @@
         <f aca="false">J204-R204</f>
         <v>-1.18</v>
       </c>
-      <c r="T204" s="13" t="e">
+      <c r="T204" s="13" t="n">
         <f aca="false">MIN(197.4,(T203+S204))</f>
-        <v>#REF!</v>
+        <v>173.383947368421</v>
       </c>
       <c r="U204" s="8" t="n">
         <v>0</v>
@@ -16189,9 +16189,9 @@
         <f aca="false">J205-R205</f>
         <v>11.595</v>
       </c>
-      <c r="T205" s="13" t="e">
+      <c r="T205" s="13" t="n">
         <f aca="false">MIN(197.4,(T204+S205))</f>
-        <v>#REF!</v>
+        <v>184.978947368421</v>
       </c>
       <c r="U205" s="45" t="s">
         <v>35</v>
@@ -16274,9 +16274,9 @@
         <f aca="false">J206-R206</f>
         <v>19.29</v>
       </c>
-      <c r="T206" s="13" t="e">
+      <c r="T206" s="13" t="n">
         <f aca="false">MIN(197.4,(T205+S206))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="U206" s="8" t="n">
         <v>0</v>
@@ -16359,9 +16359,9 @@
         <f aca="false">J207-R207</f>
         <v>-0.775</v>
       </c>
-      <c r="T207" s="13" t="e">
+      <c r="T207" s="13" t="n">
         <f aca="false">MIN(197.4,(T206+S207))</f>
-        <v>#REF!</v>
+        <v>196.625</v>
       </c>
       <c r="U207" s="45" t="s">
         <v>38</v>
@@ -16441,13 +16441,13 @@
         <f aca="false">J208-R208</f>
         <v>-0.655</v>
       </c>
-      <c r="T208" s="13" t="e">
+      <c r="T208" s="13" t="n">
         <f aca="false">MIN(197.4,(T207+S208))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U208" s="13" t="e">
+        <v>195.97</v>
+      </c>
+      <c r="U208" s="13" t="n">
         <f aca="false">MIN(T201:T221)</f>
-        <v>#REF!</v>
+        <v>171.283947368421</v>
       </c>
       <c r="V208" s="8" t="n">
         <v>1047.6</v>
@@ -16523,9 +16523,9 @@
         <f aca="false">J209-R209</f>
         <v>7.195</v>
       </c>
-      <c r="T209" s="13" t="e">
+      <c r="T209" s="13" t="n">
         <f aca="false">MIN(197.4,(T208+S209))</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="U209" s="45" t="s">
         <v>40</v>
@@ -16605,13 +16605,13 @@
         <f aca="false">J210-R210</f>
         <v>-1.34</v>
       </c>
-      <c r="T210" s="13" t="e">
+      <c r="T210" s="13" t="n">
         <f aca="false">MIN(197.4,(T209+S210))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U210" s="13" t="e">
+        <v>196.06</v>
+      </c>
+      <c r="U210" s="13" t="n">
         <f aca="false">MAX(T201:T221)</f>
-        <v>#REF!</v>
+        <v>197.4</v>
       </c>
       <c r="V210" s="8" t="n">
         <v>1009.5</v>
@@ -16688,9 +16688,9 @@
         <f aca="false">J211-R211</f>
         <v>-2.43</v>
       </c>
-      <c r="T211" s="13" t="e">
+      <c r="T211" s="13" t="n">
         <f aca="false">MIN(197.4,(T210+S211))</f>
-        <v>#REF!</v>
+        <v>193.63</v>
       </c>
       <c r="U211" s="45" t="s">
         <v>42</v>
@@ -16770,13 +16770,13 @@
         <f aca="false">J212-R212</f>
         <v>-1.265</v>
       </c>
-      <c r="T212" s="13" t="e">
+      <c r="T212" s="13" t="n">
         <f aca="false">MIN(197.4,(T211+S212))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U212" s="14" t="e">
+        <v>192.365</v>
+      </c>
+      <c r="U212" s="14" t="n">
         <f aca="false">AVERAGE(T201:T221)</f>
-        <v>#REF!</v>
+        <v>188.909035087719</v>
       </c>
       <c r="V212" s="8" t="n">
         <v>801.7</v>
@@ -16853,9 +16853,9 @@
         <f aca="false">J213-R213</f>
         <v>-0.995</v>
       </c>
-      <c r="T213" s="13" t="e">
+      <c r="T213" s="13" t="n">
         <f aca="false">MIN(197.4,(T212+S213))</f>
-        <v>#REF!</v>
+        <v>191.37</v>
       </c>
       <c r="V213" s="8" t="n">
         <v>472.7</v>
@@ -16932,13 +16932,13 @@
         <f aca="false">J214-R214</f>
         <v>0.72</v>
       </c>
-      <c r="T214" s="13" t="e">
+      <c r="T214" s="13" t="n">
         <f aca="false">MIN(197.4,(T213+S214))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U214" s="13" t="e">
+        <v>192.09</v>
+      </c>
+      <c r="U214" s="13" t="n">
         <f aca="false">(U212*100)/197.4</f>
-        <v>#REF!</v>
+        <v>95.6985993352175</v>
       </c>
       <c r="V214" s="8" t="n">
         <v>551.1</v>
@@ -17012,9 +17012,9 @@
         <f aca="false">J215-R215</f>
         <v>-1.955</v>
       </c>
-      <c r="T215" s="13" t="e">
+      <c r="T215" s="13" t="n">
         <f aca="false">MIN(197.4,(T214+S215))</f>
-        <v>#REF!</v>
+        <v>190.135</v>
       </c>
       <c r="V215" s="8" t="n">
         <v>1268.5</v>
@@ -17088,9 +17088,9 @@
         <f aca="false">J216-R216</f>
         <v>1.065</v>
       </c>
-      <c r="T216" s="13" t="e">
+      <c r="T216" s="13" t="n">
         <f aca="false">MIN(197.4,(T215+S216))</f>
-        <v>#REF!</v>
+        <v>191.2</v>
       </c>
       <c r="V216" s="8" t="n">
         <v>711.1</v>
@@ -17164,9 +17164,9 @@
         <f aca="false">J217-R217</f>
         <v>-0.57</v>
       </c>
-      <c r="T217" s="13" t="e">
+      <c r="T217" s="13" t="n">
         <f aca="false">MIN(197.4,(T216+S217))</f>
-        <v>#REF!</v>
+        <v>190.63</v>
       </c>
       <c r="V217" s="8" t="n">
         <v>1501.6</v>
@@ -17241,9 +17241,9 @@
         <f aca="false">J218-R218</f>
         <v>1.46</v>
       </c>
-      <c r="T218" s="13" t="e">
+      <c r="T218" s="13" t="n">
         <f aca="false">MIN(197.4,(T217+S218))</f>
-        <v>#REF!</v>
+        <v>192.09</v>
       </c>
       <c r="U218" s="48"/>
       <c r="V218" s="8" t="n">
@@ -17318,9 +17318,9 @@
         <f aca="false">J219-R219</f>
         <v>-0.57</v>
       </c>
-      <c r="T219" s="13" t="e">
+      <c r="T219" s="13" t="n">
         <f aca="false">MIN(197.4,(T218+S219))</f>
-        <v>#REF!</v>
+        <v>191.52</v>
       </c>
       <c r="V219" s="8" t="n">
         <v>1076.1</v>
@@ -17394,9 +17394,9 @@
         <f aca="false">J220-R220</f>
         <v>-0.38</v>
       </c>
-      <c r="T220" s="13" t="e">
+      <c r="T220" s="13" t="n">
         <f aca="false">MIN(197.4,(T219+S220))</f>
-        <v>#REF!</v>
+        <v>191.14</v>
       </c>
       <c r="V220" s="8" t="n">
         <v>675.5</v>
@@ -17472,9 +17472,9 @@
         <f aca="false">J221-R221</f>
         <v>-1.47</v>
       </c>
-      <c r="T221" s="21" t="e">
+      <c r="T221" s="21" t="n">
         <f aca="false">MIN(197.4,(T220+S221))</f>
-        <v>#REF!</v>
+        <v>189.67</v>
       </c>
       <c r="V221" s="18" t="n">
         <v>1222.2</v>
@@ -17553,9 +17553,9 @@
         <f aca="false">J222-R222</f>
         <v>-1.5</v>
       </c>
-      <c r="T222" s="13" t="e">
+      <c r="T222" s="13" t="n">
         <f aca="false">MIN(197.4,(T221+S222))</f>
-        <v>#REF!</v>
+        <v>188.17</v>
       </c>
       <c r="U222" s="53" t="s">
         <v>29</v>
@@ -17639,9 +17639,9 @@
         <f aca="false">J223-R223</f>
         <v>-2.33</v>
       </c>
-      <c r="T223" s="13" t="e">
+      <c r="T223" s="13" t="n">
         <f aca="false">MIN(197.4,(T222+S223))</f>
-        <v>#REF!</v>
+        <v>185.84</v>
       </c>
       <c r="U223" s="8" t="n">
         <v>25</v>
@@ -17725,9 +17725,9 @@
         <f aca="false">J224-R224</f>
         <v>3.38</v>
       </c>
-      <c r="T224" s="13" t="e">
+      <c r="T224" s="13" t="n">
         <f aca="false">MIN(197.4,(T223+S224))</f>
-        <v>#REF!</v>
+        <v>189.22</v>
       </c>
       <c r="U224" s="53" t="s">
         <v>32</v>
@@ -17812,9 +17812,9 @@
         <f aca="false">J225-R225</f>
         <v>-3.235</v>
       </c>
-      <c r="T225" s="13" t="e">
+      <c r="T225" s="13" t="n">
         <f aca="false">MIN(197.4,(T224+S225))</f>
-        <v>#REF!</v>
+        <v>185.985</v>
       </c>
       <c r="U225" s="8" t="n">
         <v>0</v>
@@ -17899,9 +17899,9 @@
         <f aca="false">J226-R226</f>
         <v>-2.76</v>
       </c>
-      <c r="T226" s="13" t="e">
+      <c r="T226" s="13" t="n">
         <f aca="false">MIN(197.4,(T225+S226))</f>
-        <v>#REF!</v>
+        <v>183.225</v>
       </c>
       <c r="U226" s="53" t="s">
         <v>35</v>
@@ -17986,9 +17986,9 @@
         <f aca="false">J227-R227</f>
         <v>-2.415</v>
       </c>
-      <c r="T227" s="13" t="e">
+      <c r="T227" s="13" t="n">
         <f aca="false">MIN(197.4,(T226+S227))</f>
-        <v>#REF!</v>
+        <v>180.81</v>
       </c>
       <c r="U227" s="8" t="n">
         <v>0</v>
@@ -18072,9 +18072,9 @@
         <f aca="false">J228-R228</f>
         <v>-3.68</v>
       </c>
-      <c r="T228" s="13" t="e">
+      <c r="T228" s="13" t="n">
         <f aca="false">MIN(197.4,(T227+S228))</f>
-        <v>#REF!</v>
+        <v>177.13</v>
       </c>
       <c r="U228" s="53" t="s">
         <v>38</v>
@@ -18155,13 +18155,13 @@
         <f aca="false">J229-R229</f>
         <v>-4.025</v>
       </c>
-      <c r="T229" s="13" t="e">
+      <c r="T229" s="13" t="n">
         <f aca="false">MIN(197.4,(T228+S229))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U229" s="13" t="e">
+        <v>173.105</v>
+      </c>
+      <c r="U229" s="13" t="n">
         <f aca="false">MIN(T222:T250)</f>
-        <v>#REF!</v>
+        <v>146.825</v>
       </c>
       <c r="V229" s="8" t="n">
         <v>2601.9</v>
@@ -18239,9 +18239,9 @@
         <f aca="false">J230-R230</f>
         <v>-2.405</v>
       </c>
-      <c r="T230" s="13" t="e">
+      <c r="T230" s="13" t="n">
         <f aca="false">MIN(197.4,(T229+S230))</f>
-        <v>#REF!</v>
+        <v>170.7</v>
       </c>
       <c r="U230" s="53" t="s">
         <v>40</v>
@@ -18322,13 +18322,13 @@
         <f aca="false">J231-R231</f>
         <v>7.12</v>
       </c>
-      <c r="T231" s="13" t="e">
+      <c r="T231" s="13" t="n">
         <f aca="false">MIN(197.4,(T230+S231))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U231" s="13" t="e">
+        <v>177.82</v>
+      </c>
+      <c r="U231" s="13" t="n">
         <f aca="false">MAX(T222:T250)</f>
-        <v>#REF!</v>
+        <v>189.22</v>
       </c>
       <c r="V231" s="8" t="n">
         <v>337.8</v>
@@ -18406,9 +18406,9 @@
         <f aca="false">J232-R232</f>
         <v>-0.35</v>
       </c>
-      <c r="T232" s="13" t="e">
+      <c r="T232" s="13" t="n">
         <f aca="false">MIN(197.4,(T231+S232))</f>
-        <v>#REF!</v>
+        <v>177.47</v>
       </c>
       <c r="U232" s="53" t="s">
         <v>42</v>
@@ -18489,13 +18489,13 @@
         <f aca="false">J233-R233</f>
         <v>-1.61</v>
       </c>
-      <c r="T233" s="13" t="e">
+      <c r="T233" s="13" t="n">
         <f aca="false">MIN(197.4,(T232+S233))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U233" s="14" t="e">
+        <v>175.86</v>
+      </c>
+      <c r="U233" s="14" t="n">
         <f aca="false">AVERAGE(T222:T250)</f>
-        <v>#REF!</v>
+        <v>171.317413793103</v>
       </c>
       <c r="V233" s="8" t="n">
         <v>648.7</v>
@@ -18573,9 +18573,9 @@
         <f aca="false">J234-R234</f>
         <v>-0.92</v>
       </c>
-      <c r="T234" s="13" t="e">
+      <c r="T234" s="13" t="n">
         <f aca="false">MIN(197.4,(T233+S234))</f>
-        <v>#REF!</v>
+        <v>174.94</v>
       </c>
       <c r="V234" s="8" t="n">
         <v>721.7</v>
@@ -18653,13 +18653,13 @@
         <f aca="false">J235-R235</f>
         <v>-0.595</v>
       </c>
-      <c r="T235" s="13" t="e">
+      <c r="T235" s="13" t="n">
         <f aca="false">MIN(197.4,(T234+S235))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U235" s="13" t="e">
+        <v>174.345</v>
+      </c>
+      <c r="U235" s="13" t="n">
         <f aca="false">(U233*100)/197.4</f>
-        <v>#REF!</v>
+        <v>86.7869370785732</v>
       </c>
       <c r="V235" s="8" t="n">
         <v>1063.6</v>
@@ -18734,9 +18734,9 @@
         <f aca="false">J236-R236</f>
         <v>-2.775</v>
       </c>
-      <c r="T236" s="13" t="e">
+      <c r="T236" s="13" t="n">
         <f aca="false">MIN(197.4,(T235+S236))</f>
-        <v>#REF!</v>
+        <v>171.57</v>
       </c>
       <c r="V236" s="8" t="n">
         <v>1562.2</v>
@@ -18811,9 +18811,9 @@
         <f aca="false">J237-R237</f>
         <v>-1.045</v>
       </c>
-      <c r="T237" s="13" t="e">
+      <c r="T237" s="13" t="n">
         <f aca="false">MIN(197.4,(T236+S237))</f>
-        <v>#REF!</v>
+        <v>170.525</v>
       </c>
       <c r="V237" s="8" t="n">
         <v>1637.5</v>
@@ -18888,9 +18888,9 @@
         <f aca="false">J238-R238</f>
         <v>-2.185</v>
       </c>
-      <c r="T238" s="13" t="e">
+      <c r="T238" s="13" t="n">
         <f aca="false">MIN(197.4,(T237+S238))</f>
-        <v>#REF!</v>
+        <v>168.34</v>
       </c>
       <c r="V238" s="8" t="n">
         <v>1577.1</v>
@@ -18965,9 +18965,9 @@
         <f aca="false">J239-R239</f>
         <v>12.49</v>
       </c>
-      <c r="T239" s="13" t="e">
+      <c r="T239" s="13" t="n">
         <f aca="false">MIN(197.4,(T238+S239))</f>
-        <v>#REF!</v>
+        <v>180.83</v>
       </c>
       <c r="V239" s="8" t="n">
         <v>853.1</v>
@@ -19042,9 +19042,9 @@
         <f aca="false">J240-R240</f>
         <v>-3.335</v>
       </c>
-      <c r="T240" s="13" t="e">
+      <c r="T240" s="13" t="n">
         <f aca="false">MIN(197.4,(T239+S240))</f>
-        <v>#REF!</v>
+        <v>177.495</v>
       </c>
       <c r="V240" s="8" t="n">
         <v>2004.2</v>
@@ -19119,9 +19119,9 @@
         <f aca="false">J241-R241</f>
         <v>-3.91</v>
       </c>
-      <c r="T241" s="13" t="e">
+      <c r="T241" s="13" t="n">
         <f aca="false">MIN(197.4,(T240+S241))</f>
-        <v>#REF!</v>
+        <v>173.585</v>
       </c>
       <c r="V241" s="8" t="n">
         <v>2451.7</v>
@@ -19196,9 +19196,9 @@
         <f aca="false">J242-R242</f>
         <v>-1.38</v>
       </c>
-      <c r="T242" s="13" t="e">
+      <c r="T242" s="13" t="n">
         <f aca="false">MIN(197.4,(T241+S242))</f>
-        <v>#REF!</v>
+        <v>172.205</v>
       </c>
       <c r="V242" s="8" t="n">
         <v>701.4</v>
@@ -19273,9 +19273,9 @@
         <f aca="false">J243-R243</f>
         <v>-3.565</v>
       </c>
-      <c r="T243" s="13" t="e">
+      <c r="T243" s="13" t="n">
         <f aca="false">MIN(197.4,(T242+S243))</f>
-        <v>#REF!</v>
+        <v>168.64</v>
       </c>
       <c r="V243" s="8" t="n">
         <v>2156.2</v>
@@ -19350,9 +19350,9 @@
         <f aca="false">J244-R244</f>
         <v>-5.06</v>
       </c>
-      <c r="T244" s="13" t="e">
+      <c r="T244" s="13" t="n">
         <f aca="false">MIN(197.4,(T243+S244))</f>
-        <v>#REF!</v>
+        <v>163.58</v>
       </c>
       <c r="V244" s="8" t="n">
         <v>2890.8</v>
@@ -19427,9 +19427,9 @@
         <f aca="false">J245-R245</f>
         <v>-5.865</v>
       </c>
-      <c r="T245" s="13" t="e">
+      <c r="T245" s="13" t="n">
         <f aca="false">MIN(197.4,(T244+S245))</f>
-        <v>#REF!</v>
+        <v>157.715</v>
       </c>
       <c r="V245" s="8" t="n">
         <v>2841.4</v>
@@ -19504,9 +19504,9 @@
         <f aca="false">J246-R246</f>
         <v>-3.41</v>
       </c>
-      <c r="T246" s="13" t="e">
+      <c r="T246" s="13" t="n">
         <f aca="false">MIN(197.4,(T245+S246))</f>
-        <v>#REF!</v>
+        <v>154.305</v>
       </c>
       <c r="V246" s="8" t="n">
         <v>1865.3</v>
@@ -19581,9 +19581,9 @@
         <f aca="false">J247-R247</f>
         <v>-2.65</v>
       </c>
-      <c r="T247" s="13" t="e">
+      <c r="T247" s="13" t="n">
         <f aca="false">MIN(197.4,(T246+S247))</f>
-        <v>#REF!</v>
+        <v>151.655</v>
       </c>
       <c r="V247" s="8" t="n">
         <v>1326.2</v>
@@ -19658,9 +19658,9 @@
         <f aca="false">J248-R248</f>
         <v>-4.025</v>
       </c>
-      <c r="T248" s="13" t="e">
+      <c r="T248" s="13" t="n">
         <f aca="false">MIN(197.4,(T247+S248))</f>
-        <v>#REF!</v>
+        <v>147.63</v>
       </c>
       <c r="V248" s="8" t="n">
         <v>1556.8</v>
@@ -19736,9 +19736,9 @@
         <f aca="false">J249-R249</f>
         <v>-0.805</v>
       </c>
-      <c r="T249" s="13" t="e">
+      <c r="T249" s="13" t="n">
         <f aca="false">MIN(197.4,(T248+S249))</f>
-        <v>#REF!</v>
+        <v>146.825</v>
       </c>
       <c r="U249" s="48"/>
       <c r="V249" s="8" t="n">
@@ -19816,9 +19816,9 @@
         <f aca="false">J250-R250</f>
         <v>1.86</v>
       </c>
-      <c r="T250" s="21" t="e">
+      <c r="T250" s="21" t="n">
         <f aca="false">MIN(197.4,(T249+S250))</f>
-        <v>#REF!</v>
+        <v>148.685</v>
       </c>
       <c r="V250" s="18" t="n">
         <v>823.9</v>
@@ -19898,9 +19898,9 @@
         <f aca="false">J251-R251</f>
         <v>-0.0782258064516128</v>
       </c>
-      <c r="T251" s="13" t="e">
+      <c r="T251" s="13" t="n">
         <f aca="false">MIN(197.4,(T250+S251))</f>
-        <v>#REF!</v>
+        <v>148.606774193548</v>
       </c>
       <c r="U251" s="57" t="s">
         <v>29</v>
@@ -19985,9 +19985,9 @@
         <f aca="false">J252-R252</f>
         <v>2.90064516129032</v>
       </c>
-      <c r="T252" s="13" t="e">
+      <c r="T252" s="13" t="n">
         <f aca="false">MIN(197.4,(T251+S252))</f>
-        <v>#REF!</v>
+        <v>151.507419354839</v>
       </c>
       <c r="U252" s="8" t="n">
         <v>17</v>
@@ -20072,9 +20072,9 @@
         <f aca="false">J253-R253</f>
         <v>-1.12241935483871</v>
       </c>
-      <c r="T253" s="13" t="e">
+      <c r="T253" s="13" t="n">
         <f aca="false">MIN(197.4,(T252+S253))</f>
-        <v>#REF!</v>
+        <v>150.385</v>
       </c>
       <c r="U253" s="57" t="s">
         <v>32</v>
@@ -20160,9 +20160,9 @@
         <f aca="false">J254-R254</f>
         <v>-1.86725806451613</v>
       </c>
-      <c r="T254" s="13" t="e">
+      <c r="T254" s="13" t="n">
         <f aca="false">MIN(197.4,(T253+S254))</f>
-        <v>#REF!</v>
+        <v>148.517741935484</v>
       </c>
       <c r="U254" s="8" t="n">
         <v>0</v>
@@ -20248,9 +20248,9 @@
         <f aca="false">J255-R255</f>
         <v>-2.17096774193548</v>
       </c>
-      <c r="T255" s="13" t="e">
+      <c r="T255" s="13" t="n">
         <f aca="false">MIN(197.4,(T254+S255))</f>
-        <v>#REF!</v>
+        <v>146.346774193548</v>
       </c>
       <c r="U255" s="57" t="s">
         <v>35</v>
@@ -20336,9 +20336,9 @@
         <f aca="false">J256-R256</f>
         <v>-3.11048387096774</v>
       </c>
-      <c r="T256" s="13" t="e">
+      <c r="T256" s="13" t="n">
         <f aca="false">MIN(197.4,(T255+S256))</f>
-        <v>#REF!</v>
+        <v>143.236290322581</v>
       </c>
       <c r="U256" s="8" t="n">
         <v>0</v>
@@ -20423,9 +20423,9 @@
         <f aca="false">J257-R257</f>
         <v>-1.05967741935484</v>
       </c>
-      <c r="T257" s="13" t="e">
+      <c r="T257" s="13" t="n">
         <f aca="false">MIN(197.4,(T256+S257))</f>
-        <v>#REF!</v>
+        <v>142.176612903226</v>
       </c>
       <c r="U257" s="57" t="s">
         <v>38</v>
@@ -20507,13 +20507,13 @@
         <f aca="false">J258-R258</f>
         <v>3.34387096774194</v>
       </c>
-      <c r="T258" s="13" t="e">
+      <c r="T258" s="13" t="n">
         <f aca="false">MIN(197.4,(T257+S258))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U258" s="13" t="e">
+        <v>145.520483870968</v>
+      </c>
+      <c r="U258" s="13" t="n">
         <f aca="false">MIN(T251:T272)</f>
-        <v>#REF!</v>
+        <v>134.045161290323</v>
       </c>
       <c r="V258" s="8" t="n">
         <v>754.4</v>
@@ -20592,9 +20592,9 @@
         <f aca="false">J259-R259</f>
         <v>-3.105</v>
       </c>
-      <c r="T259" s="13" t="e">
+      <c r="T259" s="13" t="n">
         <f aca="false">MIN(197.4,(T258+S259))</f>
-        <v>#REF!</v>
+        <v>142.415483870968</v>
       </c>
       <c r="U259" s="57" t="s">
         <v>40</v>
@@ -20676,13 +20676,13 @@
         <f aca="false">J260-R260</f>
         <v>-1.63354838709677</v>
       </c>
-      <c r="T260" s="13" t="e">
+      <c r="T260" s="13" t="n">
         <f aca="false">MIN(197.4,(T259+S260))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U260" s="13" t="e">
+        <v>140.781935483871</v>
+      </c>
+      <c r="U260" s="13" t="n">
         <f aca="false">MAX(T251:T272)</f>
-        <v>#REF!</v>
+        <v>151.507419354839</v>
       </c>
       <c r="V260" s="8" t="n">
         <v>786.5</v>
@@ -20761,9 +20761,9 @@
         <f aca="false">J261-R261</f>
         <v>0.57016129032258</v>
       </c>
-      <c r="T261" s="13" t="e">
+      <c r="T261" s="13" t="n">
         <f aca="false">MIN(197.4,(T260+S261))</f>
-        <v>#REF!</v>
+        <v>141.352096774194</v>
       </c>
       <c r="U261" s="57" t="s">
         <v>42</v>
@@ -20845,13 +20845,13 @@
         <f aca="false">J262-R262</f>
         <v>8.60725806451613</v>
       </c>
-      <c r="T262" s="13" t="e">
+      <c r="T262" s="13" t="n">
         <f aca="false">MIN(197.4,(T261+S262))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U262" s="14" t="e">
+        <v>149.95935483871</v>
+      </c>
+      <c r="U262" s="14" t="n">
         <f aca="false">AVERAGE(T251:T272)</f>
-        <v>#REF!</v>
+        <v>143.361209677419</v>
       </c>
       <c r="V262" s="8" t="n">
         <v>881.8</v>
@@ -20930,9 +20930,9 @@
         <f aca="false">J263-R263</f>
         <v>-2.84854838709677</v>
       </c>
-      <c r="T263" s="13" t="e">
+      <c r="T263" s="13" t="n">
         <f aca="false">MIN(197.4,(T262+S263))</f>
-        <v>#REF!</v>
+        <v>147.110806451613</v>
       </c>
       <c r="V263" s="8" t="n">
         <v>1786.8</v>
@@ -21011,13 +21011,13 @@
         <f aca="false">J264-R264</f>
         <v>-3.78048387096774</v>
       </c>
-      <c r="T264" s="13" t="e">
+      <c r="T264" s="13" t="n">
         <f aca="false">MIN(197.4,(T263+S264))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U264" s="13" t="e">
+        <v>143.330322580645</v>
+      </c>
+      <c r="U264" s="13" t="n">
         <f aca="false">(U262*100)/197.4</f>
-        <v>#REF!</v>
+        <v>72.6247262803543</v>
       </c>
       <c r="V264" s="8" t="n">
         <v>2577.1</v>
@@ -21093,9 +21093,9 @@
         <f aca="false">J265-R265</f>
         <v>-2.39112903225806</v>
       </c>
-      <c r="T265" s="13" t="e">
+      <c r="T265" s="13" t="n">
         <f aca="false">MIN(197.4,(T264+S265))</f>
-        <v>#REF!</v>
+        <v>140.939193548387</v>
       </c>
       <c r="V265" s="8" t="n">
         <v>1249.9</v>
@@ -21171,9 +21171,9 @@
         <f aca="false">J266-R266</f>
         <v>2.8241935483871</v>
       </c>
-      <c r="T266" s="13" t="e">
+      <c r="T266" s="13" t="n">
         <f aca="false">MIN(197.4,(T265+S266))</f>
-        <v>#REF!</v>
+        <v>143.763387096774</v>
       </c>
       <c r="V266" s="8" t="n">
         <v>1317.5</v>
@@ -21249,9 +21249,9 @@
         <f aca="false">J267-R267</f>
         <v>-1.48903225806452</v>
       </c>
-      <c r="T267" s="13" t="e">
+      <c r="T267" s="13" t="n">
         <f aca="false">MIN(197.4,(T266+S267))</f>
-        <v>#REF!</v>
+        <v>142.27435483871</v>
       </c>
       <c r="V267" s="8" t="n">
         <v>702.2</v>
@@ -21327,9 +21327,9 @@
         <f aca="false">J268-R268</f>
         <v>-1.31209677419355</v>
       </c>
-      <c r="T268" s="13" t="e">
+      <c r="T268" s="13" t="n">
         <f aca="false">MIN(197.4,(T267+S268))</f>
-        <v>#REF!</v>
+        <v>140.962258064516</v>
       </c>
       <c r="V268" s="8" t="n">
         <v>1894.9</v>
@@ -21405,9 +21405,9 @@
         <f aca="false">J269-R269</f>
         <v>-1.7191935483871</v>
       </c>
-      <c r="T269" s="13" t="e">
+      <c r="T269" s="13" t="n">
         <f aca="false">MIN(197.4,(T268+S269))</f>
-        <v>#REF!</v>
+        <v>139.243064516129</v>
       </c>
       <c r="V269" s="8" t="n">
         <v>1262.4</v>
@@ -21483,9 +21483,9 @@
         <f aca="false">J270-R270</f>
         <v>-2.40822580645161</v>
       </c>
-      <c r="T270" s="13" t="e">
+      <c r="T270" s="13" t="n">
         <f aca="false">MIN(197.4,(T269+S270))</f>
-        <v>#REF!</v>
+        <v>136.834838709677</v>
       </c>
       <c r="V270" s="8" t="n">
         <v>1416.6</v>
@@ -21562,9 +21562,9 @@
         <f aca="false">J271-R271</f>
         <v>-2.19758064516129</v>
       </c>
-      <c r="T271" s="13" t="e">
+      <c r="T271" s="13" t="n">
         <f aca="false">MIN(197.4,(T270+S271))</f>
-        <v>#REF!</v>
+        <v>134.637258064516</v>
       </c>
       <c r="U271" s="48"/>
       <c r="V271" s="8" t="n">
@@ -21643,9 +21643,9 @@
         <f aca="false">J272-R272</f>
         <v>-0.592096774193548</v>
       </c>
-      <c r="T272" s="21" t="e">
+      <c r="T272" s="21" t="n">
         <f aca="false">MIN(197.4,(T271+S272))</f>
-        <v>#REF!</v>
+        <v>134.045161290323</v>
       </c>
       <c r="V272" s="18" t="n">
         <v>1420.3</v>
@@ -21725,9 +21725,9 @@
         <f aca="false">J273-R273</f>
         <v>-1.0091935483871</v>
       </c>
-      <c r="T273" s="13" t="e">
+      <c r="T273" s="13" t="n">
         <f aca="false">MIN(197.4,(T272+S273))</f>
-        <v>#REF!</v>
+        <v>133.035967741936</v>
       </c>
       <c r="U273" s="62" t="s">
         <v>29</v>
@@ -21812,9 +21812,9 @@
         <f aca="false">J274-R274</f>
         <v>-1.26048387096774</v>
       </c>
-      <c r="T274" s="13" t="e">
+      <c r="T274" s="13" t="n">
         <f aca="false">MIN(197.4,(T273+S274))</f>
-        <v>#REF!</v>
+        <v>131.775483870968</v>
       </c>
       <c r="U274" s="8" t="n">
         <v>14</v>
@@ -21899,9 +21899,9 @@
         <f aca="false">J275-R275</f>
         <v>-1.32387096774194</v>
       </c>
-      <c r="T275" s="13" t="e">
+      <c r="T275" s="13" t="n">
         <f aca="false">MIN(197.4,(T274+S275))</f>
-        <v>#REF!</v>
+        <v>130.451612903226</v>
       </c>
       <c r="U275" s="62" t="s">
         <v>32</v>
@@ -21987,9 +21987,9 @@
         <f aca="false">J276-R276</f>
         <v>-1.46612903225806</v>
       </c>
-      <c r="T276" s="13" t="e">
+      <c r="T276" s="13" t="n">
         <f aca="false">MIN(197.4,(T275+S276))</f>
-        <v>#REF!</v>
+        <v>128.985483870968</v>
       </c>
       <c r="U276" s="8" t="n">
         <v>0</v>
@@ -22075,9 +22075,9 @@
         <f aca="false">J277-R277</f>
         <v>-1.20241935483871</v>
       </c>
-      <c r="T277" s="13" t="e">
+      <c r="T277" s="13" t="n">
         <f aca="false">MIN(197.4,(T276+S277))</f>
-        <v>#REF!</v>
+        <v>127.783064516129</v>
       </c>
       <c r="U277" s="62" t="s">
         <v>35</v>
@@ -22163,9 +22163,9 @@
         <f aca="false">J278-R278</f>
         <v>-2.76048387096774</v>
       </c>
-      <c r="T278" s="13" t="e">
+      <c r="T278" s="13" t="n">
         <f aca="false">MIN(197.4,(T277+S278))</f>
-        <v>#REF!</v>
+        <v>125.022580645161</v>
       </c>
       <c r="U278" s="8" t="n">
         <v>0</v>
@@ -22250,9 +22250,9 @@
         <f aca="false">J279-R279</f>
         <v>-3.33596774193548</v>
       </c>
-      <c r="T279" s="13" t="e">
+      <c r="T279" s="13" t="n">
         <f aca="false">MIN(197.4,(T278+S279))</f>
-        <v>#REF!</v>
+        <v>121.686612903226</v>
       </c>
       <c r="U279" s="62" t="s">
         <v>38</v>
@@ -22334,13 +22334,13 @@
         <f aca="false">J280-R280</f>
         <v>-3.05161290322581</v>
       </c>
-      <c r="T280" s="13" t="e">
+      <c r="T280" s="13" t="n">
         <f aca="false">MIN(197.4,(T279+S280))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U280" s="13" t="e">
+        <v>118.635</v>
+      </c>
+      <c r="U280" s="13" t="n">
         <f aca="false">MIN(T273:T297)</f>
-        <v>#REF!</v>
+        <v>118.635</v>
       </c>
       <c r="V280" s="8" t="n">
         <v>2085.6</v>
@@ -22419,9 +22419,9 @@
         <f aca="false">J281-R281</f>
         <v>7.125</v>
       </c>
-      <c r="T281" s="13" t="e">
+      <c r="T281" s="13" t="n">
         <f aca="false">MIN(197.4,(T280+S281))</f>
-        <v>#REF!</v>
+        <v>125.76</v>
       </c>
       <c r="U281" s="62" t="s">
         <v>40</v>
@@ -22503,13 +22503,13 @@
         <f aca="false">J282-R282</f>
         <v>3.24177419354839</v>
       </c>
-      <c r="T282" s="13" t="e">
+      <c r="T282" s="13" t="n">
         <f aca="false">MIN(197.4,(T281+S282))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U282" s="13" t="e">
+        <v>129.001774193548</v>
+      </c>
+      <c r="U282" s="13" t="n">
         <f aca="false">MAX(T273:T297)</f>
-        <v>#REF!</v>
+        <v>190.160161290323</v>
       </c>
       <c r="V282" s="8" t="n">
         <v>612.1</v>
@@ -22588,9 +22588,9 @@
         <f aca="false">J283-R283</f>
         <v>0.930967741935484</v>
       </c>
-      <c r="T283" s="13" t="e">
+      <c r="T283" s="13" t="n">
         <f aca="false">MIN(197.4,(T282+S283))</f>
-        <v>#REF!</v>
+        <v>129.932741935484</v>
       </c>
       <c r="U283" s="62" t="s">
         <v>42</v>
@@ -22672,13 +22672,13 @@
         <f aca="false">J284-R284</f>
         <v>5.4041935483871</v>
       </c>
-      <c r="T284" s="13" t="e">
+      <c r="T284" s="13" t="n">
         <f aca="false">MIN(197.4,(T283+S284))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U284" s="14" t="e">
+        <v>135.336935483871</v>
+      </c>
+      <c r="U284" s="14" t="n">
         <f aca="false">AVERAGE(T273:T297)</f>
-        <v>#REF!</v>
+        <v>150.127135483871</v>
       </c>
       <c r="V284" s="8" t="n">
         <v>539.7</v>
@@ -22757,9 +22757,9 @@
         <f aca="false">J285-R285</f>
         <v>14.7429032258065</v>
       </c>
-      <c r="T285" s="13" t="e">
+      <c r="T285" s="13" t="n">
         <f aca="false">MIN(197.4,(T284+S285))</f>
-        <v>#REF!</v>
+        <v>150.079838709678</v>
       </c>
       <c r="V285" s="8" t="n">
         <v>874.5</v>
@@ -22838,13 +22838,13 @@
         <f aca="false">J286-R286</f>
         <v>5.70887096774194</v>
       </c>
-      <c r="T286" s="13" t="e">
+      <c r="T286" s="13" t="n">
         <f aca="false">MIN(197.4,(T285+S286))</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U286" s="13" t="e">
+        <v>155.788709677419</v>
+      </c>
+      <c r="U286" s="13" t="n">
         <f aca="false">(U284*100)/197.4</f>
-        <v>#REF!</v>
+        <v>76.0522469523156</v>
       </c>
       <c r="V286" s="8" t="n">
         <v>679.6</v>
@@ -22920,9 +22920,9 @@
         <f aca="false">J287-R287</f>
         <v>-1.15225806451613</v>
       </c>
-      <c r="T287" s="13" t="e">
+      <c r="T287" s="13" t="n">
         <f aca="false">MIN(197.4,(T286+S287))</f>
-        <v>#REF!</v>
+        <v>154.636451612903</v>
       </c>
       <c r="V287" s="8" t="n">
         <v>1931.1</v>
@@ -22998,9 +22998,9 @@
         <f aca="false">J288-R288</f>
         <v>2.90838709677419</v>
       </c>
-      <c r="T288" s="13" t="e">
+      <c r="T288" s="13" t="n">
         <f aca="false">MIN(197.4,(T287+S288))</f>
-        <v>#REF!</v>
+        <v>157.544838709678</v>
       </c>
       <c r="V288" s="8" t="n">
         <v>722.3</v>
@@ -23076,9 +23076,9 @@
         <f aca="false">J289-R289</f>
         <v>-1.03483870967742</v>
       </c>
-      <c r="T289" s="13" t="e">
+      <c r="T289" s="13" t="n">
         <f aca="false">MIN(197.4,(T288+S289))</f>
-        <v>#REF!</v>
+        <v>156.51</v>
       </c>
       <c r="V289" s="8" t="n">
         <v>866.8</v>
@@ -23154,9 +23154,9 @@
         <f aca="false">J290-R290</f>
         <v>4.87596774193548</v>
       </c>
-      <c r="T290" s="13" t="e">
+      <c r="T290" s="13" t="n">
         <f aca="false">MIN(197.4,(T289+S290))</f>
-        <v>#REF!</v>
+        <v>161.385967741936</v>
       </c>
       <c r="V290" s="8" t="n">
         <v>680.7</v>
@@ -23232,9 +23232,9 @@
         <f aca="false">J291-R291</f>
         <v>8.91693548387097</v>
       </c>
-      <c r="T291" s="13" t="e">
+      <c r="T291" s="13" t="n">
         <f aca="false">MIN(197.4,(T290+S291))</f>
-        <v>#REF!</v>
+        <v>170.302903225807</v>
       </c>
       <c r="V291" s="8" t="n">
         <v>392.6</v>
@@ -23310,9 +23310,9 @@
         <f aca="false">J292-R292</f>
         <v>-0.790483870967742</v>
       </c>
-      <c r="T292" s="13" t="e">
+      <c r="T292" s="13" t="n">
         <f aca="false">MIN(197.4,(T291+S292))</f>
-        <v>#REF!</v>
+        <v>169.512419354839</v>
       </c>
       <c r="V292" s="8" t="n">
         <v>516.5</v>
@@ -23388,9 +23388,9 @@
         <f aca="false">J293-R293</f>
         <v>20.5287096774194</v>
       </c>
-      <c r="T293" s="13" t="e">
+      <c r="T293" s="13" t="n">
         <f aca="false">MIN(197.4,(T292+S293))</f>
-        <v>#REF!</v>
+        <v>190.041129032258</v>
       </c>
       <c r="V293" s="8" t="n">
         <v>813.4</v>
@@ -23466,9 +23466,9 @@
         <f aca="false">J294-R294</f>
         <v>0.119032258064516</v>
       </c>
-      <c r="T294" s="13" t="e">
+      <c r="T294" s="13" t="n">
         <f aca="false">MIN(197.4,(T293+S294))</f>
-        <v>#REF!</v>
+        <v>190.160161290323</v>
       </c>
       <c r="V294" s="8" t="n">
         <v>884.1</v>
@@ -23544,9 +23544,9 @@
         <f aca="false">J295-R295</f>
         <v>-2.16354838709677</v>
       </c>
-      <c r="T295" s="13" t="e">
+      <c r="T295" s="13" t="n">
         <f aca="false">MIN(197.4,(T294+S295))</f>
-        <v>#REF!</v>
+        <v>187.996612903226</v>
       </c>
       <c r="V295" s="8" t="n">
         <v>2097.3</v>
@@ -23623,9 +23623,9 @@
         <f aca="false">J296-R296</f>
         <v>-1.40241935483871</v>
       </c>
-      <c r="T296" s="13" t="e">
+      <c r="T296" s="13" t="n">
         <f aca="false">MIN(197.4,(T295+S296))</f>
-        <v>#REF!</v>
+        <v>186.594193548387</v>
       </c>
       <c r="V296" s="8" t="n">
         <v>1640.4</v>
@@ -23703,9 +23703,9 @@
         <f aca="false">J297-R297</f>
         <v>-1.37629032258064</v>
       </c>
-      <c r="T297" s="21" t="e">
+      <c r="T297" s="21" t="n">
         <f aca="false">MIN(197.4,(T296+S297))</f>
-        <v>#REF!</v>
+        <v>185.217903225807</v>
       </c>
       <c r="V297" s="18" t="n">
         <v>1648.4</v>
@@ -23780,9 +23780,9 @@
         <f aca="false">J298-R298</f>
         <v>1.41629032258065</v>
       </c>
-      <c r="T298" s="13" t="e">
+      <c r="T298" s="13" t="n">
         <f aca="false">MIN(197.4,(T297+S298))</f>
-        <v>#REF!</v>
+        <v>186.634193548387</v>
       </c>
       <c r="V298" s="8" t="n">
         <v>495</v>
@@ -23857,9 +23857,9 @@
         <f aca="false">J299-R299</f>
         <v>-0.994354838709677</v>
       </c>
-      <c r="T299" s="13" t="e">
+      <c r="T299" s="13" t="n">
         <f aca="false">MIN(197.4,(T298+S299))</f>
-        <v>#REF!</v>
+        <v>185.639838709678</v>
       </c>
       <c r="V299" s="8" t="n">
         <v>1261</v>
@@ -23935,9 +23935,9 @@
         <f aca="false">J300-R300</f>
         <v>-1.01258064516129</v>
       </c>
-      <c r="T300" s="13" t="e">
+      <c r="T300" s="13" t="n">
         <f aca="false">MIN(197.4,(T299+S300))</f>
-        <v>#REF!</v>
+        <v>184.627258064516</v>
       </c>
       <c r="V300" s="8" t="n">
         <v>1435.5</v>
@@ -24013,9 +24013,9 @@
         <f aca="false">J301-R301</f>
         <v>-0.685483870967742</v>
       </c>
-      <c r="T301" s="13" t="e">
+      <c r="T301" s="13" t="n">
         <f aca="false">MIN(197.4,(T300+S301))</f>
-        <v>#REF!</v>
+        <v>183.941774193549</v>
       </c>
       <c r="V301" s="8" t="n">
         <v>769.2</v>
@@ -24091,9 +24091,9 @@
         <f aca="false">J302-R302</f>
         <v>-0.458064516129032</v>
       </c>
-      <c r="T302" s="13" t="e">
+      <c r="T302" s="13" t="n">
         <f aca="false">MIN(197.4,(T301+S302))</f>
-        <v>#REF!</v>
+        <v>183.483709677419</v>
       </c>
       <c r="V302" s="8" t="n">
         <v>714.9</v>
@@ -24169,9 +24169,9 @@
         <f aca="false">J303-R303</f>
         <v>-0.158548387096774</v>
       </c>
-      <c r="T303" s="13" t="e">
+      <c r="T303" s="13" t="n">
         <f aca="false">MIN(197.4,(T302+S303))</f>
-        <v>#REF!</v>
+        <v>183.325161290323</v>
       </c>
       <c r="V303" s="8" t="n">
         <v>1495.7</v>
@@ -24247,9 +24247,9 @@
         <f aca="false">J304-R304</f>
         <v>1.15612903225806</v>
       </c>
-      <c r="T304" s="13" t="e">
+      <c r="T304" s="13" t="n">
         <f aca="false">MIN(197.4,(T303+S304))</f>
-        <v>#REF!</v>
+        <v>184.481290322581</v>
       </c>
       <c r="V304" s="8" t="n">
         <v>537.6</v>
@@ -24325,9 +24325,9 @@
         <f aca="false">J305-R305</f>
         <v>-0.704516129032258</v>
       </c>
-      <c r="T305" s="13" t="e">
+      <c r="T305" s="13" t="n">
         <f aca="false">MIN(197.4,(T304+S305))</f>
-        <v>#REF!</v>
+        <v>183.776774193549</v>
       </c>
       <c r="V305" s="8" t="n">
         <v>726.3</v>
@@ -24403,9 +24403,9 @@
         <f aca="false">J306-R306</f>
         <v>-0.726612903225806</v>
       </c>
-      <c r="T306" s="13" t="e">
+      <c r="T306" s="13" t="n">
         <f aca="false">MIN(197.4,(T305+S306))</f>
-        <v>#REF!</v>
+        <v>183.050161290323</v>
       </c>
       <c r="V306" s="8" t="n">
         <v>840.4</v>
@@ -24481,9 +24481,9 @@
         <f aca="false">J307-R307</f>
         <v>-2.11403225806452</v>
       </c>
-      <c r="T307" s="13" t="e">
+      <c r="T307" s="13" t="n">
         <f aca="false">MIN(197.4,(T306+S307))</f>
-        <v>#REF!</v>
+        <v>180.936129032258</v>
       </c>
       <c r="V307" s="8" t="n">
         <v>2909.6</v>
@@ -24559,9 +24559,9 @@
         <f aca="false">J308-R308</f>
         <v>-2.32935483870968</v>
       </c>
-      <c r="T308" s="13" t="e">
+      <c r="T308" s="13" t="n">
         <f aca="false">MIN(197.4,(T307+S308))</f>
-        <v>#REF!</v>
+        <v>178.606774193549</v>
       </c>
       <c r="V308" s="8" t="n">
         <v>2991.2</v>
@@ -24637,9 +24637,9 @@
         <f aca="false">J309-R309</f>
         <v>-1.55483870967742</v>
       </c>
-      <c r="T309" s="13" t="e">
+      <c r="T309" s="13" t="n">
         <f aca="false">MIN(197.4,(T308+S309))</f>
-        <v>#REF!</v>
+        <v>177.051935483871</v>
       </c>
       <c r="V309" s="8" t="n">
         <v>2104.1</v>
@@ -24715,9 +24715,9 @@
         <f aca="false">J310-R310</f>
         <v>-0.751612903225806</v>
       </c>
-      <c r="T310" s="13" t="e">
+      <c r="T310" s="13" t="n">
         <f aca="false">MIN(197.4,(T309+S310))</f>
-        <v>#REF!</v>
+        <v>176.300322580645</v>
       </c>
       <c r="V310" s="8" t="n">
         <v>910.5</v>
@@ -24793,9 +24793,9 @@
         <f aca="false">J311-R311</f>
         <v>-0.544354838709678</v>
       </c>
-      <c r="T311" s="13" t="e">
+      <c r="T311" s="13" t="n">
         <f aca="false">MIN(197.4,(T310+S311))</f>
-        <v>#REF!</v>
+        <v>175.755967741936</v>
       </c>
       <c r="V311" s="8" t="n">
         <v>655.4</v>
@@ -24871,9 +24871,9 @@
         <f aca="false">J312-R312</f>
         <v>-1.295</v>
       </c>
-      <c r="T312" s="13" t="e">
+      <c r="T312" s="13" t="n">
         <f aca="false">MIN(197.4,(T311+S312))</f>
-        <v>#REF!</v>
+        <v>174.460967741936</v>
       </c>
       <c r="V312" s="8" t="n">
         <v>1836.3</v>
